--- a/data/data_distritos.xlsx
+++ b/data/data_distritos.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D202"/>
+  <dimension ref="A1:D242"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4">
@@ -505,7 +505,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>179</v>
+        <v>136</v>
       </c>
     </row>
     <row r="5">
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>636</v>
+        <v>607</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>459</v>
+        <v>439</v>
       </c>
     </row>
     <row r="8">
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1829</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="10">
@@ -613,7 +613,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>192</v>
+        <v>143</v>
       </c>
     </row>
     <row r="11">
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>321</v>
+        <v>292</v>
       </c>
     </row>
     <row r="12">
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>127</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13">
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>141</v>
+        <v>52</v>
       </c>
     </row>
     <row r="14">
@@ -685,7 +685,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>144</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15">
@@ -721,7 +721,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>111</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17">
@@ -739,7 +739,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>87</v>
+        <v>58</v>
       </c>
     </row>
     <row r="18">
@@ -775,7 +775,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>829</v>
+        <v>341</v>
       </c>
     </row>
     <row r="20">
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>294</v>
+        <v>92</v>
       </c>
     </row>
     <row r="21">
@@ -811,7 +811,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>38</v>
+        <v>21</v>
       </c>
     </row>
     <row r="22">
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>42</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23">
@@ -847,7 +847,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="24">
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>102</v>
+        <v>93</v>
       </c>
     </row>
     <row r="25">
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>413</v>
+        <v>319</v>
       </c>
     </row>
     <row r="26">
@@ -901,7 +901,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>169</v>
+        <v>140</v>
       </c>
     </row>
     <row r="27">
@@ -919,7 +919,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>150</v>
+        <v>70</v>
       </c>
     </row>
     <row r="28">
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>81</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29">
@@ -955,7 +955,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="30">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>65</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -1027,7 +1027,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>279</v>
+        <v>248</v>
       </c>
     </row>
     <row r="34">
@@ -1081,7 +1081,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -1099,7 +1099,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="38">
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>72</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40">
@@ -1153,7 +1153,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="41">
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="42">
@@ -1207,7 +1207,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>36</v>
+        <v>4</v>
       </c>
     </row>
     <row r="44">
@@ -1225,7 +1225,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>263</v>
+        <v>260</v>
       </c>
     </row>
     <row r="45">
@@ -1261,7 +1261,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>87</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47">
@@ -1279,7 +1279,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>147</v>
+        <v>77</v>
       </c>
     </row>
     <row r="48">
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>134</v>
+        <v>86</v>
       </c>
     </row>
     <row r="49">
@@ -1311,11 +1311,11 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>HEROES ALBARRACIN</t>
+          <t>ILABAYA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>34</v>
+        <v>184</v>
       </c>
     </row>
     <row r="50">
@@ -1329,29 +1329,29 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ILABAYA</t>
+          <t>SAMA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>234</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>TACNA</t>
+          <t>AMAZONAS</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>SAMA</t>
+          <t>QUINJALCA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>72</v>
+        <v>38</v>
       </c>
     </row>
     <row r="52">
@@ -1365,11 +1365,11 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>QUINJALCA</t>
+          <t>SONCHE</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>38</v>
+        <v>13</v>
       </c>
     </row>
     <row r="53">
@@ -1378,16 +1378,16 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>AMAZONAS</t>
+          <t>ANCASH</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>SONCHE</t>
+          <t>ANRA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>13</v>
+        <v>202</v>
       </c>
     </row>
     <row r="54">
@@ -1401,11 +1401,11 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ANRA</t>
+          <t>CHAVIN DE HUANTAR</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>202</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="55">
@@ -1419,11 +1419,11 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>CHAVIN DE HUANTAR</t>
+          <t>COTAPARACO</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1878</v>
+        <v>31</v>
       </c>
     </row>
     <row r="56">
@@ -1437,11 +1437,11 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>COTAPARACO</t>
+          <t>PONTO</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>31</v>
+        <v>425</v>
       </c>
     </row>
     <row r="57">
@@ -1455,11 +1455,11 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>PONTO</t>
+          <t>RAHUAPAMPA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>425</v>
+        <v>115</v>
       </c>
     </row>
     <row r="58">
@@ -1473,11 +1473,11 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>RAHUAPAMPA</t>
+          <t>SAN MARCOS</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>115</v>
+        <v>3379</v>
       </c>
     </row>
     <row r="59">
@@ -1486,16 +1486,16 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ANCASH</t>
+          <t>AREQUIPA</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>SAN MARCOS</t>
+          <t>CHAPARRA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>3379</v>
+        <v>231</v>
       </c>
     </row>
     <row r="60">
@@ -1509,11 +1509,11 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>CHAPARRA</t>
+          <t>MARIANO NICOLAS VALCARCEL</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>231</v>
+        <v>436</v>
       </c>
     </row>
     <row r="61">
@@ -1527,11 +1527,11 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>MARIANO NICOLAS VALCARCEL</t>
+          <t>MOLLEBAYA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>436</v>
+        <v>68</v>
       </c>
     </row>
     <row r="62">
@@ -1545,11 +1545,11 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>MOLLEBAYA</t>
+          <t>QUEQUEÑA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>68</v>
+        <v>167</v>
       </c>
     </row>
     <row r="63">
@@ -1563,11 +1563,11 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>QUEQUEÑA</t>
+          <t>YARABAMBA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>167</v>
+        <v>204</v>
       </c>
     </row>
     <row r="64">
@@ -1576,16 +1576,16 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>AYACUCHO</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>YARABAMBA</t>
+          <t>COLTA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>204</v>
+        <v>102</v>
       </c>
     </row>
     <row r="65">
@@ -1599,11 +1599,11 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>COLTA</t>
+          <t>HUAC-HUAS</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>102</v>
+        <v>75</v>
       </c>
     </row>
     <row r="66">
@@ -1617,11 +1617,11 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>HUAC-HUAS</t>
+          <t>HUANCARAYLLA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>75</v>
+        <v>175</v>
       </c>
     </row>
     <row r="67">
@@ -1630,16 +1630,16 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>AYACUCHO</t>
+          <t>CAJAMARCA</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>HUANCARAYLLA</t>
+          <t>ANDABAMBA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>175</v>
+        <v>29</v>
       </c>
     </row>
     <row r="68">
@@ -1648,16 +1648,16 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>CAJAMARCA</t>
+          <t>CUSCO</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>ANDABAMBA</t>
+          <t>PICHARI</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>29</v>
+        <v>974</v>
       </c>
     </row>
     <row r="69">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>PICHARI</t>
+          <t>SAYLLA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>974</v>
+        <v>233</v>
       </c>
     </row>
     <row r="70">
@@ -1684,16 +1684,16 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>CUSCO</t>
+          <t>HUANCAVELICA</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>SAYLLA</t>
+          <t>HUAYACUNDO ARMA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>233</v>
+        <v>39</v>
       </c>
     </row>
     <row r="71">
@@ -1707,11 +1707,11 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>HUAYACUNDO ARMA</t>
+          <t>PILCHACA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>39</v>
+        <v>19</v>
       </c>
     </row>
     <row r="72">
@@ -1725,11 +1725,11 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>PILCHACA</t>
+          <t>TAMBO</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>19</v>
+        <v>82</v>
       </c>
     </row>
     <row r="73">
@@ -1738,16 +1738,16 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>HUANCAVELICA</t>
+          <t>HUANUCO</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>TAMBO</t>
+          <t>CAHUAC</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>82</v>
+        <v>132</v>
       </c>
     </row>
     <row r="74">
@@ -1761,11 +1761,11 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>CAHUAC</t>
+          <t>CASTILLO GRANDE</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>132</v>
+        <v>187</v>
       </c>
     </row>
     <row r="75">
@@ -1779,11 +1779,11 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>CASTILLO GRANDE</t>
+          <t>CHACABAMBA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>187</v>
+        <v>230</v>
       </c>
     </row>
     <row r="76">
@@ -1797,11 +1797,11 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>CHACABAMBA</t>
+          <t>LA MORADA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>230</v>
+        <v>153</v>
       </c>
     </row>
     <row r="77">
@@ -1815,11 +1815,11 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>LA MORADA</t>
+          <t>PAMPAMARCA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>153</v>
+        <v>189</v>
       </c>
     </row>
     <row r="78">
@@ -1833,11 +1833,11 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>PAMPAMARCA</t>
+          <t>SANTA ROSA DE ALTO YANAJANCA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>189</v>
+        <v>14</v>
       </c>
     </row>
     <row r="79">
@@ -1851,11 +1851,11 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>SANTA ROSA DE ALTO YANAJANCA</t>
+          <t>YARUMAYO</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>14</v>
+        <v>200</v>
       </c>
     </row>
     <row r="80">
@@ -1864,16 +1864,16 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>HUANUCO</t>
+          <t>JUNIN</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>YARUMAYO</t>
+          <t>MARCAPOMACOCHA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>200</v>
+        <v>26</v>
       </c>
     </row>
     <row r="81">
@@ -1887,11 +1887,11 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>MARCAPOMACOCHA</t>
+          <t>VIZCATAN DEL ENE</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>26</v>
+        <v>519</v>
       </c>
     </row>
     <row r="82">
@@ -1900,16 +1900,16 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>LIMA</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>VIZCATAN DEL ENE</t>
+          <t>ALIS</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>519</v>
+        <v>80</v>
       </c>
     </row>
     <row r="83">
@@ -1923,11 +1923,11 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>ALIS</t>
+          <t>ALLAUCA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>80</v>
+        <v>125</v>
       </c>
     </row>
     <row r="84">
@@ -1941,11 +1941,11 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>ALLAUCA</t>
+          <t>AZANGARO</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>125</v>
+        <v>68</v>
       </c>
     </row>
     <row r="85">
@@ -1959,11 +1959,11 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>AZANGARO</t>
+          <t>CARANIA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>68</v>
+        <v>30</v>
       </c>
     </row>
     <row r="86">
@@ -1977,11 +1977,11 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>CARANIA</t>
+          <t>HUAMPARA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>30</v>
+        <v>71</v>
       </c>
     </row>
     <row r="87">
@@ -1995,11 +1995,11 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>HUAMPARA</t>
+          <t>HUANGASCAR</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>71</v>
+        <v>85</v>
       </c>
     </row>
     <row r="88">
@@ -2013,11 +2013,11 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>HUANGASCAR</t>
+          <t>LARAOS</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>85</v>
+        <v>36</v>
       </c>
     </row>
     <row r="89">
@@ -2031,11 +2031,11 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>LARAOS</t>
+          <t>PUTINZA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
     </row>
     <row r="90">
@@ -2049,11 +2049,11 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>PUTINZA</t>
+          <t>TOMAS</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>9</v>
+        <v>34</v>
       </c>
     </row>
     <row r="91">
@@ -2062,16 +2062,16 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>LIMA</t>
+          <t>LORETO</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>TOMAS</t>
+          <t>SOPLIN</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
@@ -2085,11 +2085,11 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>SOPLIN</t>
+          <t>TAPICHE</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>1</v>
+        <v>210</v>
       </c>
     </row>
     <row r="93">
@@ -2098,16 +2098,16 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>LORETO</t>
+          <t>MADRE DE DIOS</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>TAPICHE</t>
+          <t>TAHUAMANU</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>210</v>
+        <v>70</v>
       </c>
     </row>
     <row r="94">
@@ -2116,16 +2116,16 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>MOQUEGUA</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>TAHUAMANU</t>
+          <t>EL ALGARROBAL</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>70</v>
+        <v>608</v>
       </c>
     </row>
     <row r="95">
@@ -2134,16 +2134,16 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>MOQUEGUA</t>
+          <t>PASCO</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>EL ALGARROBAL</t>
+          <t>CHACAYAN</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>608</v>
+        <v>102</v>
       </c>
     </row>
     <row r="96">
@@ -2157,11 +2157,11 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>CHACAYAN</t>
+          <t>GOYLLARISQUIZGA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>102</v>
+        <v>23</v>
       </c>
     </row>
     <row r="97">
@@ -2170,16 +2170,16 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>PASCO</t>
+          <t>PUNO</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>GOYLLARISQUIZGA</t>
+          <t>LIMBANI</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>23</v>
+        <v>175</v>
       </c>
     </row>
     <row r="98">
@@ -2188,16 +2188,16 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>PUNO</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>LIMBANI</t>
+          <t>SHUNTE</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>175</v>
+        <v>204</v>
       </c>
     </row>
     <row r="99">
@@ -2206,16 +2206,16 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>SAN MARTIN</t>
+          <t>TACNA</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>SHUNTE</t>
+          <t>HEROES ALBARRACIN</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>204</v>
+        <v>135</v>
       </c>
     </row>
     <row r="100">
@@ -2229,11 +2229,11 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>HEROES ALBARRACIN</t>
+          <t>ILABAYA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>135</v>
+        <v>547</v>
       </c>
     </row>
     <row r="101">
@@ -2247,29 +2247,29 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>ILABAYA</t>
+          <t>SAMA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>547</v>
+        <v>81</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>46094</v>
+        <v>46095</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>TACNA</t>
+          <t>AMAZONAS</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>SAMA</t>
+          <t>QUINJALCA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="103">
@@ -2283,11 +2283,11 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>QUINJALCA</t>
+          <t>SONCHE</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>76</v>
+        <v>25</v>
       </c>
     </row>
     <row r="104">
@@ -2296,16 +2296,16 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>AMAZONAS</t>
+          <t>ANCASH</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>SONCHE</t>
+          <t>ANRA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>25</v>
+        <v>246</v>
       </c>
     </row>
     <row r="105">
@@ -2319,11 +2319,11 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>ANRA</t>
+          <t>CHAVIN DE HUANTAR</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>246</v>
+        <v>2177</v>
       </c>
     </row>
     <row r="106">
@@ -2337,11 +2337,11 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>CHAVIN DE HUANTAR</t>
+          <t>COTAPARACO</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>2177</v>
+        <v>49</v>
       </c>
     </row>
     <row r="107">
@@ -2355,11 +2355,11 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>COTAPARACO</t>
+          <t>PONTO</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>49</v>
+        <v>266</v>
       </c>
     </row>
     <row r="108">
@@ -2373,11 +2373,11 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>PONTO</t>
+          <t>RAHUAPAMPA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>266</v>
+        <v>58</v>
       </c>
     </row>
     <row r="109">
@@ -2391,11 +2391,11 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>RAHUAPAMPA</t>
+          <t>SAN MARCOS</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>58</v>
+        <v>3151</v>
       </c>
     </row>
     <row r="110">
@@ -2404,16 +2404,16 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>ANCASH</t>
+          <t>AREQUIPA</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>SAN MARCOS</t>
+          <t>CHAPARRA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>3151</v>
+        <v>151</v>
       </c>
     </row>
     <row r="111">
@@ -2427,11 +2427,11 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>CHAPARRA</t>
+          <t>MARIANO NICOLAS VALCARCEL</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>151</v>
+        <v>343</v>
       </c>
     </row>
     <row r="112">
@@ -2445,11 +2445,11 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>MARIANO NICOLAS VALCARCEL</t>
+          <t>MOLLEBAYA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>343</v>
+        <v>220</v>
       </c>
     </row>
     <row r="113">
@@ -2463,11 +2463,11 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>MOLLEBAYA</t>
+          <t>QUEQUEÑA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>220</v>
+        <v>343</v>
       </c>
     </row>
     <row r="114">
@@ -2481,11 +2481,11 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>QUEQUEÑA</t>
+          <t>YARABAMBA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>343</v>
+        <v>419</v>
       </c>
     </row>
     <row r="115">
@@ -2494,16 +2494,16 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>AYACUCHO</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>YARABAMBA</t>
+          <t>COLTA</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>419</v>
+        <v>90</v>
       </c>
     </row>
     <row r="116">
@@ -2517,11 +2517,11 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>COLTA</t>
+          <t>HUAC-HUAS</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>90</v>
+        <v>145</v>
       </c>
     </row>
     <row r="117">
@@ -2535,11 +2535,11 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>HUAC-HUAS</t>
+          <t>HUANCARAYLLA</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>145</v>
+        <v>219</v>
       </c>
     </row>
     <row r="118">
@@ -2548,16 +2548,16 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>AYACUCHO</t>
+          <t>CAJAMARCA</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>HUANCARAYLLA</t>
+          <t>ANDABAMBA</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>219</v>
+        <v>17</v>
       </c>
     </row>
     <row r="119">
@@ -2566,16 +2566,16 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>CAJAMARCA</t>
+          <t>CUSCO</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>ANDABAMBA</t>
+          <t>PICHARI</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>17</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="120">
@@ -2589,11 +2589,11 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>PICHARI</t>
+          <t>SAYLLA</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>1176</v>
+        <v>297</v>
       </c>
     </row>
     <row r="121">
@@ -2602,16 +2602,16 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>CUSCO</t>
+          <t>HUANCAVELICA</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>SAYLLA</t>
+          <t>HUAYACUNDO ARMA</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>297</v>
+        <v>61</v>
       </c>
     </row>
     <row r="122">
@@ -2625,11 +2625,11 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>HUAYACUNDO ARMA</t>
+          <t>PILCHACA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>61</v>
+        <v>27</v>
       </c>
     </row>
     <row r="123">
@@ -2643,11 +2643,11 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>PILCHACA</t>
+          <t>TAMBO</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>27</v>
+        <v>201</v>
       </c>
     </row>
     <row r="124">
@@ -2656,16 +2656,16 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>HUANCAVELICA</t>
+          <t>HUANUCO</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>TAMBO</t>
+          <t>CAHUAC</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>201</v>
+        <v>151</v>
       </c>
     </row>
     <row r="125">
@@ -2679,11 +2679,11 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>CAHUAC</t>
+          <t>CASTILLO GRANDE</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>151</v>
+        <v>808</v>
       </c>
     </row>
     <row r="126">
@@ -2697,11 +2697,11 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>CASTILLO GRANDE</t>
+          <t>CHACABAMBA</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>808</v>
+        <v>280</v>
       </c>
     </row>
     <row r="127">
@@ -2715,11 +2715,11 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>CHACABAMBA</t>
+          <t>LA MORADA</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>280</v>
+        <v>175</v>
       </c>
     </row>
     <row r="128">
@@ -2733,11 +2733,11 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>LA MORADA</t>
+          <t>PAMPAMARCA</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>175</v>
+        <v>166</v>
       </c>
     </row>
     <row r="129">
@@ -2751,11 +2751,11 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>PAMPAMARCA</t>
+          <t>SANTA ROSA DE ALTO YANAJANCA</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>166</v>
+        <v>71</v>
       </c>
     </row>
     <row r="130">
@@ -2769,11 +2769,11 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>SANTA ROSA DE ALTO YANAJANCA</t>
+          <t>YARUMAYO</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>71</v>
+        <v>201</v>
       </c>
     </row>
     <row r="131">
@@ -2782,16 +2782,16 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>HUANUCO</t>
+          <t>JUNIN</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>YARUMAYO</t>
+          <t>MARCAPOMACOCHA</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>201</v>
+        <v>214</v>
       </c>
     </row>
     <row r="132">
@@ -2805,11 +2805,11 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>MARCAPOMACOCHA</t>
+          <t>VIZCATAN DEL ENE</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>214</v>
+        <v>566</v>
       </c>
     </row>
     <row r="133">
@@ -2818,16 +2818,16 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>LIMA</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>VIZCATAN DEL ENE</t>
+          <t>ALIS</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>566</v>
+        <v>76</v>
       </c>
     </row>
     <row r="134">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>ALIS</t>
+          <t>ALLAUCA</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>76</v>
+        <v>106</v>
       </c>
     </row>
     <row r="135">
@@ -2859,11 +2859,11 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>ALLAUCA</t>
+          <t>AZANGARO</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>106</v>
+        <v>75</v>
       </c>
     </row>
     <row r="136">
@@ -2877,11 +2877,11 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>AZANGARO</t>
+          <t>CARANIA</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>75</v>
+        <v>20</v>
       </c>
     </row>
     <row r="137">
@@ -2895,11 +2895,11 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>CARANIA</t>
+          <t>HUAMPARA</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="138">
@@ -2913,11 +2913,11 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>HUAMPARA</t>
+          <t>HUANGASCAR</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>17</v>
+        <v>144</v>
       </c>
     </row>
     <row r="139">
@@ -2931,11 +2931,11 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>HUANGASCAR</t>
+          <t>LARAOS</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>144</v>
+        <v>113</v>
       </c>
     </row>
     <row r="140">
@@ -2949,11 +2949,11 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>LARAOS</t>
+          <t>PUTINZA</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>113</v>
+        <v>22</v>
       </c>
     </row>
     <row r="141">
@@ -2967,11 +2967,11 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>PUTINZA</t>
+          <t>TOMAS</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>22</v>
+        <v>42</v>
       </c>
     </row>
     <row r="142">
@@ -2980,16 +2980,16 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>LIMA</t>
+          <t>LORETO</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>TOMAS</t>
+          <t>SOPLIN</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>42</v>
+        <v>160</v>
       </c>
     </row>
     <row r="143">
@@ -3003,11 +3003,11 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>SOPLIN</t>
+          <t>TAPICHE</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>160</v>
+        <v>58</v>
       </c>
     </row>
     <row r="144">
@@ -3016,16 +3016,16 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>LORETO</t>
+          <t>MADRE DE DIOS</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>TAPICHE</t>
+          <t>TAHUAMANU</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>58</v>
+        <v>105</v>
       </c>
     </row>
     <row r="145">
@@ -3034,16 +3034,16 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>MOQUEGUA</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>TAHUAMANU</t>
+          <t>EL ALGARROBAL</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>105</v>
+        <v>502</v>
       </c>
     </row>
     <row r="146">
@@ -3052,16 +3052,16 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>MOQUEGUA</t>
+          <t>PASCO</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>EL ALGARROBAL</t>
+          <t>CHACAYAN</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>502</v>
+        <v>196</v>
       </c>
     </row>
     <row r="147">
@@ -3075,11 +3075,11 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>CHACAYAN</t>
+          <t>GOYLLARISQUIZGA</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>196</v>
+        <v>29</v>
       </c>
     </row>
     <row r="148">
@@ -3088,16 +3088,16 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>PASCO</t>
+          <t>PUNO</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>GOYLLARISQUIZGA</t>
+          <t>LIMBANI</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>29</v>
+        <v>292</v>
       </c>
     </row>
     <row r="149">
@@ -3106,16 +3106,16 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>PUNO</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>LIMBANI</t>
+          <t>SHUNTE</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>292</v>
+        <v>149</v>
       </c>
     </row>
     <row r="150">
@@ -3124,16 +3124,16 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>SAN MARTIN</t>
+          <t>TACNA</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>SHUNTE</t>
+          <t>HEROES ALBARRACIN</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>149</v>
+        <v>83</v>
       </c>
     </row>
     <row r="151">
@@ -3147,11 +3147,11 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>HEROES ALBARRACIN</t>
+          <t>ILABAYA</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>83</v>
+        <v>575</v>
       </c>
     </row>
     <row r="152">
@@ -3165,29 +3165,29 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>ILABAYA</t>
+          <t>SAMA</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>575</v>
+        <v>147</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="n">
-        <v>46095</v>
+        <v>46096</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>TACNA</t>
+          <t>AMAZONAS</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>SAMA</t>
+          <t>QUINJALCA</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>147</v>
+        <v>46</v>
       </c>
     </row>
     <row r="154">
@@ -3201,11 +3201,11 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>QUINJALCA</t>
+          <t>SONCHE</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
     </row>
     <row r="155">
@@ -3214,16 +3214,16 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>AMAZONAS</t>
+          <t>ANCASH</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>SONCHE</t>
+          <t>ANRA</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>23</v>
+        <v>125</v>
       </c>
     </row>
     <row r="156">
@@ -3237,11 +3237,11 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>ANRA</t>
+          <t>CHAVIN DE HUANTAR</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>125</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="157">
@@ -3255,11 +3255,11 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>CHAVIN DE HUANTAR</t>
+          <t>COTAPARACO</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>1428</v>
+        <v>17</v>
       </c>
     </row>
     <row r="158">
@@ -3273,11 +3273,11 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>COTAPARACO</t>
+          <t>PONTO</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>17</v>
+        <v>481</v>
       </c>
     </row>
     <row r="159">
@@ -3291,11 +3291,11 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>PONTO</t>
+          <t>RAHUAPAMPA</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>481</v>
+        <v>114</v>
       </c>
     </row>
     <row r="160">
@@ -3309,11 +3309,11 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>RAHUAPAMPA</t>
+          <t>SAN MARCOS</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>114</v>
+        <v>2239</v>
       </c>
     </row>
     <row r="161">
@@ -3322,16 +3322,16 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>ANCASH</t>
+          <t>AREQUIPA</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>SAN MARCOS</t>
+          <t>CHAPARRA</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>2239</v>
+        <v>137</v>
       </c>
     </row>
     <row r="162">
@@ -3345,11 +3345,11 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>CHAPARRA</t>
+          <t>MARIANO NICOLAS VALCARCEL</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>137</v>
+        <v>146</v>
       </c>
     </row>
     <row r="163">
@@ -3363,11 +3363,11 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>MARIANO NICOLAS VALCARCEL</t>
+          <t>MOLLEBAYA</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>146</v>
+        <v>132</v>
       </c>
     </row>
     <row r="164">
@@ -3381,11 +3381,11 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>MOLLEBAYA</t>
+          <t>QUEQUEÑA</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>132</v>
+        <v>238</v>
       </c>
     </row>
     <row r="165">
@@ -3399,11 +3399,11 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>QUEQUEÑA</t>
+          <t>YARABAMBA</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>238</v>
+        <v>265</v>
       </c>
     </row>
     <row r="166">
@@ -3412,16 +3412,16 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>AYACUCHO</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>YARABAMBA</t>
+          <t>COLTA</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>265</v>
+        <v>6</v>
       </c>
     </row>
     <row r="167">
@@ -3435,11 +3435,11 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>COLTA</t>
+          <t>HUAC-HUAS</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>6</v>
+        <v>150</v>
       </c>
     </row>
     <row r="168">
@@ -3453,11 +3453,11 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>HUAC-HUAS</t>
+          <t>HUANCARAYLLA</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>150</v>
+        <v>215</v>
       </c>
     </row>
     <row r="169">
@@ -3466,16 +3466,16 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>AYACUCHO</t>
+          <t>CUSCO</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>HUANCARAYLLA</t>
+          <t>PICHARI</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>215</v>
+        <v>894</v>
       </c>
     </row>
     <row r="170">
@@ -3489,11 +3489,11 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>PICHARI</t>
+          <t>SAYLLA</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>894</v>
+        <v>300</v>
       </c>
     </row>
     <row r="171">
@@ -3502,16 +3502,16 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>CUSCO</t>
+          <t>HUANCAVELICA</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>SAYLLA</t>
+          <t>HUAYACUNDO ARMA</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>300</v>
+        <v>28</v>
       </c>
     </row>
     <row r="172">
@@ -3525,11 +3525,11 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>HUAYACUNDO ARMA</t>
+          <t>PILCHACA</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>28</v>
+        <v>266</v>
       </c>
     </row>
     <row r="173">
@@ -3543,11 +3543,11 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>PILCHACA</t>
+          <t>TAMBO</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>266</v>
+        <v>49</v>
       </c>
     </row>
     <row r="174">
@@ -3556,16 +3556,16 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>HUANCAVELICA</t>
+          <t>HUANUCO</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>TAMBO</t>
+          <t>CAHUAC</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>49</v>
+        <v>61</v>
       </c>
     </row>
     <row r="175">
@@ -3579,11 +3579,11 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>CAHUAC</t>
+          <t>CASTILLO GRANDE</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>61</v>
+        <v>852</v>
       </c>
     </row>
     <row r="176">
@@ -3597,11 +3597,11 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>CASTILLO GRANDE</t>
+          <t>CHACABAMBA</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>852</v>
+        <v>279</v>
       </c>
     </row>
     <row r="177">
@@ -3615,11 +3615,11 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>CHACABAMBA</t>
+          <t>LA MORADA</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>279</v>
+        <v>151</v>
       </c>
     </row>
     <row r="178">
@@ -3633,11 +3633,11 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>LA MORADA</t>
+          <t>PAMPAMARCA</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>151</v>
+        <v>331</v>
       </c>
     </row>
     <row r="179">
@@ -3651,11 +3651,11 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>PAMPAMARCA</t>
+          <t>SANTA ROSA DE ALTO YANAJANCA</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>331</v>
+        <v>50</v>
       </c>
     </row>
     <row r="180">
@@ -3669,11 +3669,11 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>SANTA ROSA DE ALTO YANAJANCA</t>
+          <t>YARUMAYO</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>50</v>
+        <v>215</v>
       </c>
     </row>
     <row r="181">
@@ -3682,16 +3682,16 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>HUANUCO</t>
+          <t>JUNIN</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>YARUMAYO</t>
+          <t>MARCAPOMACOCHA</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>215</v>
+        <v>209</v>
       </c>
     </row>
     <row r="182">
@@ -3705,11 +3705,11 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>MARCAPOMACOCHA</t>
+          <t>VIZCATAN DEL ENE</t>
         </is>
       </c>
       <c r="D182" t="n">
-        <v>209</v>
+        <v>139</v>
       </c>
     </row>
     <row r="183">
@@ -3718,16 +3718,16 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>LIMA</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>VIZCATAN DEL ENE</t>
+          <t>ALIS</t>
         </is>
       </c>
       <c r="D183" t="n">
-        <v>139</v>
+        <v>7</v>
       </c>
     </row>
     <row r="184">
@@ -3741,11 +3741,11 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>ALIS</t>
+          <t>ALLAUCA</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>7</v>
+        <v>31</v>
       </c>
     </row>
     <row r="185">
@@ -3759,11 +3759,11 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>ALLAUCA</t>
+          <t>AZANGARO</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
     </row>
     <row r="186">
@@ -3777,11 +3777,11 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>AZANGARO</t>
+          <t>HUAMPARA</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>4</v>
+        <v>66</v>
       </c>
     </row>
     <row r="187">
@@ -3795,11 +3795,11 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>HUAMPARA</t>
+          <t>HUANGASCAR</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>66</v>
+        <v>42</v>
       </c>
     </row>
     <row r="188">
@@ -3813,11 +3813,11 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>HUANGASCAR</t>
+          <t>LARAOS</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>42</v>
+        <v>22</v>
       </c>
     </row>
     <row r="189">
@@ -3831,11 +3831,11 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>LARAOS</t>
+          <t>PUTINZA</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
     </row>
     <row r="190">
@@ -3849,11 +3849,11 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>PUTINZA</t>
+          <t>TOMAS</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>14</v>
+        <v>51</v>
       </c>
     </row>
     <row r="191">
@@ -3862,16 +3862,16 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>LIMA</t>
+          <t>LORETO</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>TOMAS</t>
+          <t>SOPLIN</t>
         </is>
       </c>
       <c r="D191" t="n">
-        <v>51</v>
+        <v>90</v>
       </c>
     </row>
     <row r="192">
@@ -3885,11 +3885,11 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>SOPLIN</t>
+          <t>TAPICHE</t>
         </is>
       </c>
       <c r="D192" t="n">
-        <v>90</v>
+        <v>23</v>
       </c>
     </row>
     <row r="193">
@@ -3898,16 +3898,16 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>LORETO</t>
+          <t>MADRE DE DIOS</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>TAPICHE</t>
+          <t>TAHUAMANU</t>
         </is>
       </c>
       <c r="D193" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
     </row>
     <row r="194">
@@ -3916,16 +3916,16 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>MOQUEGUA</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>TAHUAMANU</t>
+          <t>EL ALGARROBAL</t>
         </is>
       </c>
       <c r="D194" t="n">
-        <v>35</v>
+        <v>374</v>
       </c>
     </row>
     <row r="195">
@@ -3934,16 +3934,16 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>MOQUEGUA</t>
+          <t>PASCO</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>EL ALGARROBAL</t>
+          <t>CHACAYAN</t>
         </is>
       </c>
       <c r="D195" t="n">
-        <v>374</v>
+        <v>201</v>
       </c>
     </row>
     <row r="196">
@@ -3957,11 +3957,11 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>CHACAYAN</t>
+          <t>GOYLLARISQUIZGA</t>
         </is>
       </c>
       <c r="D196" t="n">
-        <v>201</v>
+        <v>91</v>
       </c>
     </row>
     <row r="197">
@@ -3970,16 +3970,16 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>PASCO</t>
+          <t>PUNO</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>GOYLLARISQUIZGA</t>
+          <t>LIMBANI</t>
         </is>
       </c>
       <c r="D197" t="n">
-        <v>91</v>
+        <v>391</v>
       </c>
     </row>
     <row r="198">
@@ -3988,16 +3988,16 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>PUNO</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>LIMBANI</t>
+          <t>SHUNTE</t>
         </is>
       </c>
       <c r="D198" t="n">
-        <v>391</v>
+        <v>54</v>
       </c>
     </row>
     <row r="199">
@@ -4006,16 +4006,16 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>SAN MARTIN</t>
+          <t>TACNA</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>SHUNTE</t>
+          <t>HEROES ALBARRACIN</t>
         </is>
       </c>
       <c r="D199" t="n">
-        <v>54</v>
+        <v>119</v>
       </c>
     </row>
     <row r="200">
@@ -4029,11 +4029,11 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>HEROES ALBARRACIN</t>
+          <t>ILABAYA</t>
         </is>
       </c>
       <c r="D200" t="n">
-        <v>119</v>
+        <v>533</v>
       </c>
     </row>
     <row r="201">
@@ -4047,29 +4047,749 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>ILABAYA</t>
+          <t>SAMA</t>
         </is>
       </c>
       <c r="D201" t="n">
-        <v>533</v>
+        <v>202</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="n">
-        <v>46096</v>
+        <v>46097</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
+          <t>AMAZONAS</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>SONCHE</t>
+        </is>
+      </c>
+      <c r="D202" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>ANRA</t>
+        </is>
+      </c>
+      <c r="D203" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>CHAVIN DE HUANTAR</t>
+        </is>
+      </c>
+      <c r="D204" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>PONTO</t>
+        </is>
+      </c>
+      <c r="D205" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>SAN MARCOS</t>
+        </is>
+      </c>
+      <c r="D206" t="n">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>CHAPARRA</t>
+        </is>
+      </c>
+      <c r="D207" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>MARIANO NICOLAS VALCARCEL</t>
+        </is>
+      </c>
+      <c r="D208" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>MOLLEBAYA</t>
+        </is>
+      </c>
+      <c r="D209" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>QUEQUEÑA</t>
+        </is>
+      </c>
+      <c r="D210" t="n">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>YARABAMBA</t>
+        </is>
+      </c>
+      <c r="D211" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>HUAC-HUAS</t>
+        </is>
+      </c>
+      <c r="D212" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>HUANCARAYLLA</t>
+        </is>
+      </c>
+      <c r="D213" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>CUSCO</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>PICHARI</t>
+        </is>
+      </c>
+      <c r="D214" t="n">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>CUSCO</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>SAYLLA</t>
+        </is>
+      </c>
+      <c r="D215" t="n">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>HUAYACUNDO ARMA</t>
+        </is>
+      </c>
+      <c r="D216" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>PILCHACA</t>
+        </is>
+      </c>
+      <c r="D217" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>TAMBO</t>
+        </is>
+      </c>
+      <c r="D218" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>CAHUAC</t>
+        </is>
+      </c>
+      <c r="D219" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>CASTILLO GRANDE</t>
+        </is>
+      </c>
+      <c r="D220" t="n">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>CHACABAMBA</t>
+        </is>
+      </c>
+      <c r="D221" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>LA MORADA</t>
+        </is>
+      </c>
+      <c r="D222" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>SANTA ROSA DE ALTO YANAJANCA</t>
+        </is>
+      </c>
+      <c r="D223" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>YARUMAYO</t>
+        </is>
+      </c>
+      <c r="D224" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>MARCAPOMACOCHA</t>
+        </is>
+      </c>
+      <c r="D225" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>ALLAUCA</t>
+        </is>
+      </c>
+      <c r="D226" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>HUAMPARA</t>
+        </is>
+      </c>
+      <c r="D227" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>HUANGASCAR</t>
+        </is>
+      </c>
+      <c r="D228" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>PUTINZA</t>
+        </is>
+      </c>
+      <c r="D229" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>TOMAS</t>
+        </is>
+      </c>
+      <c r="D230" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>LORETO</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>SOPLIN</t>
+        </is>
+      </c>
+      <c r="D231" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>TAHUAMANU</t>
+        </is>
+      </c>
+      <c r="D232" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>MOQUEGUA</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>EL ALGARROBAL</t>
+        </is>
+      </c>
+      <c r="D233" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>PASCO</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>GOYLLARISQUIZGA</t>
+        </is>
+      </c>
+      <c r="D234" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>LIMBANI</t>
+        </is>
+      </c>
+      <c r="D235" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>SHUNTE</t>
+        </is>
+      </c>
+      <c r="D236" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
           <t>TACNA</t>
         </is>
       </c>
-      <c r="C202" t="inlineStr">
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>HEROES ALBARRACIN</t>
+        </is>
+      </c>
+      <c r="D237" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>ILABAYA</t>
+        </is>
+      </c>
+      <c r="D238" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
         <is>
           <t>SAMA</t>
         </is>
       </c>
-      <c r="D202" t="n">
-        <v>202</v>
+      <c r="D239" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>PONTO</t>
+        </is>
+      </c>
+      <c r="D240" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>SAN MARCOS</t>
+        </is>
+      </c>
+      <c r="D241" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>MOQUEGUA</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>EL ALGARROBAL</t>
+        </is>
+      </c>
+      <c r="D242" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/data/data_distritos.xlsx
+++ b/data/data_distritos.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D242"/>
+  <dimension ref="A1:D267"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>607</v>
+        <v>610</v>
       </c>
     </row>
     <row r="6">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7">
@@ -559,7 +559,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>439</v>
+        <v>503</v>
       </c>
     </row>
     <row r="8">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>56</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9">
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1212</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="10">
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="12">
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13">
@@ -775,7 +775,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="20">
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>319</v>
+        <v>332</v>
       </c>
     </row>
     <row r="26">
@@ -901,7 +901,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>140</v>
+        <v>176</v>
       </c>
     </row>
     <row r="27">
@@ -933,11 +933,11 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>SANTA ROSA DE ALTO YANAJANCA</t>
+          <t>PAMPAMARCA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29">
@@ -951,11 +951,11 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>YARUMAYO</t>
+          <t>SANTA ROSA DE ALTO YANAJANCA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>178</v>
+        <v>21</v>
       </c>
     </row>
     <row r="30">
@@ -964,16 +964,16 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>HUANUCO</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>MARCAPOMACOCHA</t>
+          <t>YARUMAYO</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>178</v>
       </c>
     </row>
     <row r="31">
@@ -987,11 +987,11 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>VIZCATAN DEL ENE</t>
+          <t>MARCAPOMACOCHA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>152</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -1000,16 +1000,16 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>LIMA</t>
+          <t>JUNIN</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ALIS</t>
+          <t>VIZCATAN DEL ENE</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>20</v>
+        <v>152</v>
       </c>
     </row>
     <row r="33">
@@ -1023,11 +1023,11 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ALLAUCA</t>
+          <t>ALIS</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>248</v>
+        <v>20</v>
       </c>
     </row>
     <row r="34">
@@ -1041,11 +1041,11 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>AZANGARO</t>
+          <t>ALLAUCA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>126</v>
+        <v>261</v>
       </c>
     </row>
     <row r="35">
@@ -1059,11 +1059,11 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CARANIA</t>
+          <t>AZANGARO</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>24</v>
+        <v>126</v>
       </c>
     </row>
     <row r="36">
@@ -1077,11 +1077,11 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>HUAMPARA</t>
+          <t>CARANIA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="37">
@@ -1095,11 +1095,11 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>HUANGASCAR</t>
+          <t>HUAMPARA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -1113,11 +1113,11 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>LARAOS</t>
+          <t>HUANGASCAR</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="39">
@@ -1131,11 +1131,11 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>PUTINZA</t>
+          <t>LARAOS</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="40">
@@ -1149,11 +1149,11 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>TOMAS</t>
+          <t>PUTINZA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>34</v>
+        <v>16</v>
       </c>
     </row>
     <row r="41">
@@ -1162,16 +1162,16 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>LORETO</t>
+          <t>LIMA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>SOPLIN</t>
+          <t>TOMAS</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>51</v>
+        <v>34</v>
       </c>
     </row>
     <row r="42">
@@ -1185,11 +1185,11 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>TAPICHE</t>
+          <t>SOPLIN</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>173</v>
+        <v>51</v>
       </c>
     </row>
     <row r="43">
@@ -1198,16 +1198,16 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>LORETO</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>TAHUAMANU</t>
+          <t>TAPICHE</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>4</v>
+        <v>173</v>
       </c>
     </row>
     <row r="44">
@@ -1216,16 +1216,16 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>MOQUEGUA</t>
+          <t>MADRE DE DIOS</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>EL ALGARROBAL</t>
+          <t>TAHUAMANU</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>260</v>
+        <v>4</v>
       </c>
     </row>
     <row r="45">
@@ -1234,16 +1234,16 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>PASCO</t>
+          <t>MOQUEGUA</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>CHACAYAN</t>
+          <t>EL ALGARROBAL</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>14</v>
+        <v>268</v>
       </c>
     </row>
     <row r="46">
@@ -1257,11 +1257,11 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>GOYLLARISQUIZGA</t>
+          <t>CHACAYAN</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="47">
@@ -1270,16 +1270,16 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>PUNO</t>
+          <t>PASCO</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>LIMBANI</t>
+          <t>GOYLLARISQUIZGA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>77</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48">
@@ -1288,16 +1288,16 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SAN MARTIN</t>
+          <t>PUNO</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>SHUNTE</t>
+          <t>LIMBANI</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>86</v>
+        <v>77</v>
       </c>
     </row>
     <row r="49">
@@ -1306,16 +1306,16 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>TACNA</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ILABAYA</t>
+          <t>SHUNTE</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>184</v>
+        <v>86</v>
       </c>
     </row>
     <row r="50">
@@ -1329,29 +1329,29 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>SAMA</t>
+          <t>ILABAYA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>3</v>
+        <v>188</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>46094</v>
+        <v>46093</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>AMAZONAS</t>
+          <t>TACNA</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>QUINJALCA</t>
+          <t>SAMA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>38</v>
+        <v>18</v>
       </c>
     </row>
     <row r="52">
@@ -1365,11 +1365,11 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>SONCHE</t>
+          <t>QUINJALCA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>13</v>
+        <v>38</v>
       </c>
     </row>
     <row r="53">
@@ -1378,16 +1378,16 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ANCASH</t>
+          <t>AMAZONAS</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ANRA</t>
+          <t>SONCHE</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>202</v>
+        <v>13</v>
       </c>
     </row>
     <row r="54">
@@ -1401,11 +1401,11 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>CHAVIN DE HUANTAR</t>
+          <t>ANRA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1878</v>
+        <v>203</v>
       </c>
     </row>
     <row r="55">
@@ -1419,11 +1419,11 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>COTAPARACO</t>
+          <t>CHAVIN DE HUANTAR</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>31</v>
+        <v>1881</v>
       </c>
     </row>
     <row r="56">
@@ -1437,11 +1437,11 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>PONTO</t>
+          <t>COTAPARACO</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>425</v>
+        <v>31</v>
       </c>
     </row>
     <row r="57">
@@ -1455,11 +1455,11 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>RAHUAPAMPA</t>
+          <t>PONTO</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>115</v>
+        <v>468</v>
       </c>
     </row>
     <row r="58">
@@ -1473,11 +1473,11 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>SAN MARCOS</t>
+          <t>RAHUAPAMPA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>3379</v>
+        <v>157</v>
       </c>
     </row>
     <row r="59">
@@ -1486,16 +1486,16 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>ANCASH</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>CHAPARRA</t>
+          <t>SAN MARCOS</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>231</v>
+        <v>3511</v>
       </c>
     </row>
     <row r="60">
@@ -1509,11 +1509,11 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>MARIANO NICOLAS VALCARCEL</t>
+          <t>CHAPARRA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>436</v>
+        <v>231</v>
       </c>
     </row>
     <row r="61">
@@ -1527,11 +1527,11 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>MOLLEBAYA</t>
+          <t>MARIANO NICOLAS VALCARCEL</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>68</v>
+        <v>437</v>
       </c>
     </row>
     <row r="62">
@@ -1545,11 +1545,11 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>QUEQUEÑA</t>
+          <t>MOLLEBAYA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>167</v>
+        <v>105</v>
       </c>
     </row>
     <row r="63">
@@ -1563,11 +1563,11 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>YARABAMBA</t>
+          <t>QUEQUEÑA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>204</v>
+        <v>167</v>
       </c>
     </row>
     <row r="64">
@@ -1576,16 +1576,16 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>AYACUCHO</t>
+          <t>AREQUIPA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>COLTA</t>
+          <t>YARABAMBA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>102</v>
+        <v>208</v>
       </c>
     </row>
     <row r="65">
@@ -1599,11 +1599,11 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>HUAC-HUAS</t>
+          <t>COLTA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>75</v>
+        <v>102</v>
       </c>
     </row>
     <row r="66">
@@ -1617,11 +1617,11 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>HUANCARAYLLA</t>
+          <t>HUAC-HUAS</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>175</v>
+        <v>75</v>
       </c>
     </row>
     <row r="67">
@@ -1630,16 +1630,16 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>CAJAMARCA</t>
+          <t>AYACUCHO</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>ANDABAMBA</t>
+          <t>HUANCARAYLLA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>29</v>
+        <v>175</v>
       </c>
     </row>
     <row r="68">
@@ -1648,16 +1648,16 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>CUSCO</t>
+          <t>CAJAMARCA</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>PICHARI</t>
+          <t>ANDABAMBA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>974</v>
+        <v>29</v>
       </c>
     </row>
     <row r="69">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>SAYLLA</t>
+          <t>PICHARI</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>233</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="70">
@@ -1684,16 +1684,16 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>HUANCAVELICA</t>
+          <t>CUSCO</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>HUAYACUNDO ARMA</t>
+          <t>SAYLLA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>39</v>
+        <v>233</v>
       </c>
     </row>
     <row r="71">
@@ -1707,11 +1707,11 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>PILCHACA</t>
+          <t>HUAYACUNDO ARMA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>19</v>
+        <v>39</v>
       </c>
     </row>
     <row r="72">
@@ -1725,11 +1725,11 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>TAMBO</t>
+          <t>PILCHACA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>82</v>
+        <v>19</v>
       </c>
     </row>
     <row r="73">
@@ -1738,16 +1738,16 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>HUANUCO</t>
+          <t>HUANCAVELICA</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>CAHUAC</t>
+          <t>TAMBO</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>132</v>
+        <v>82</v>
       </c>
     </row>
     <row r="74">
@@ -1761,11 +1761,11 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>CASTILLO GRANDE</t>
+          <t>CAHUAC</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>187</v>
+        <v>139</v>
       </c>
     </row>
     <row r="75">
@@ -1779,11 +1779,11 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>CHACABAMBA</t>
+          <t>CASTILLO GRANDE</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>230</v>
+        <v>195</v>
       </c>
     </row>
     <row r="76">
@@ -1797,11 +1797,11 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>LA MORADA</t>
+          <t>CHACABAMBA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>153</v>
+        <v>253</v>
       </c>
     </row>
     <row r="77">
@@ -1815,11 +1815,11 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>PAMPAMARCA</t>
+          <t>LA MORADA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>189</v>
+        <v>153</v>
       </c>
     </row>
     <row r="78">
@@ -1833,11 +1833,11 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>SANTA ROSA DE ALTO YANAJANCA</t>
+          <t>PAMPAMARCA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>14</v>
+        <v>189</v>
       </c>
     </row>
     <row r="79">
@@ -1851,11 +1851,11 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>YARUMAYO</t>
+          <t>SANTA ROSA DE ALTO YANAJANCA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>200</v>
+        <v>14</v>
       </c>
     </row>
     <row r="80">
@@ -1864,16 +1864,16 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>HUANUCO</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>MARCAPOMACOCHA</t>
+          <t>YARUMAYO</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>26</v>
+        <v>218</v>
       </c>
     </row>
     <row r="81">
@@ -1887,11 +1887,11 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>VIZCATAN DEL ENE</t>
+          <t>MARCAPOMACOCHA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>519</v>
+        <v>26</v>
       </c>
     </row>
     <row r="82">
@@ -1900,16 +1900,16 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>LIMA</t>
+          <t>JUNIN</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>ALIS</t>
+          <t>VIZCATAN DEL ENE</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>80</v>
+        <v>534</v>
       </c>
     </row>
     <row r="83">
@@ -1923,11 +1923,11 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>ALLAUCA</t>
+          <t>ALIS</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>125</v>
+        <v>80</v>
       </c>
     </row>
     <row r="84">
@@ -1941,11 +1941,11 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>AZANGARO</t>
+          <t>ALLAUCA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>68</v>
+        <v>127</v>
       </c>
     </row>
     <row r="85">
@@ -1959,11 +1959,11 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>CARANIA</t>
+          <t>AZANGARO</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>30</v>
+        <v>68</v>
       </c>
     </row>
     <row r="86">
@@ -1977,11 +1977,11 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>HUAMPARA</t>
+          <t>CARANIA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>71</v>
+        <v>30</v>
       </c>
     </row>
     <row r="87">
@@ -1995,11 +1995,11 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>HUANGASCAR</t>
+          <t>HUAMPARA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>85</v>
+        <v>71</v>
       </c>
     </row>
     <row r="88">
@@ -2013,11 +2013,11 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>LARAOS</t>
+          <t>HUANGASCAR</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>36</v>
+        <v>85</v>
       </c>
     </row>
     <row r="89">
@@ -2031,11 +2031,11 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>PUTINZA</t>
+          <t>LARAOS</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>9</v>
+        <v>36</v>
       </c>
     </row>
     <row r="90">
@@ -2049,11 +2049,11 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>TOMAS</t>
+          <t>PUTINZA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>34</v>
+        <v>19</v>
       </c>
     </row>
     <row r="91">
@@ -2062,16 +2062,16 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>LORETO</t>
+          <t>LIMA</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>SOPLIN</t>
+          <t>TOMAS</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
     </row>
     <row r="92">
@@ -2085,11 +2085,11 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>TAPICHE</t>
+          <t>SOPLIN</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>210</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
@@ -2098,16 +2098,16 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>LORETO</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>TAHUAMANU</t>
+          <t>TAPICHE</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>70</v>
+        <v>287</v>
       </c>
     </row>
     <row r="94">
@@ -2116,16 +2116,16 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>MOQUEGUA</t>
+          <t>MADRE DE DIOS</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>EL ALGARROBAL</t>
+          <t>TAHUAMANU</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>608</v>
+        <v>70</v>
       </c>
     </row>
     <row r="95">
@@ -2134,16 +2134,16 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>PASCO</t>
+          <t>MOQUEGUA</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>CHACAYAN</t>
+          <t>EL ALGARROBAL</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>102</v>
+        <v>632</v>
       </c>
     </row>
     <row r="96">
@@ -2157,11 +2157,11 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>GOYLLARISQUIZGA</t>
+          <t>CHACAYAN</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>23</v>
+        <v>102</v>
       </c>
     </row>
     <row r="97">
@@ -2170,16 +2170,16 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>PUNO</t>
+          <t>PASCO</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>LIMBANI</t>
+          <t>GOYLLARISQUIZGA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>175</v>
+        <v>23</v>
       </c>
     </row>
     <row r="98">
@@ -2188,16 +2188,16 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>SAN MARTIN</t>
+          <t>PUNO</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>SHUNTE</t>
+          <t>LIMBANI</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>204</v>
+        <v>175</v>
       </c>
     </row>
     <row r="99">
@@ -2206,16 +2206,16 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>TACNA</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>HEROES ALBARRACIN</t>
+          <t>SHUNTE</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>135</v>
+        <v>204</v>
       </c>
     </row>
     <row r="100">
@@ -2229,11 +2229,11 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>ILABAYA</t>
+          <t>HEROES ALBARRACIN</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>547</v>
+        <v>135</v>
       </c>
     </row>
     <row r="101">
@@ -2247,29 +2247,29 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>SAMA</t>
+          <t>ILABAYA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>81</v>
+        <v>563</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>46095</v>
+        <v>46094</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>AMAZONAS</t>
+          <t>TACNA</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>QUINJALCA</t>
+          <t>SAMA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>76</v>
+        <v>117</v>
       </c>
     </row>
     <row r="103">
@@ -2283,11 +2283,11 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>SONCHE</t>
+          <t>QUINJALCA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>25</v>
+        <v>76</v>
       </c>
     </row>
     <row r="104">
@@ -2296,16 +2296,16 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>ANCASH</t>
+          <t>AMAZONAS</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>ANRA</t>
+          <t>SONCHE</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>246</v>
+        <v>25</v>
       </c>
     </row>
     <row r="105">
@@ -2319,11 +2319,11 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>CHAVIN DE HUANTAR</t>
+          <t>ANRA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>2177</v>
+        <v>246</v>
       </c>
     </row>
     <row r="106">
@@ -2337,11 +2337,11 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>COTAPARACO</t>
+          <t>CHAVIN DE HUANTAR</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>49</v>
+        <v>2212</v>
       </c>
     </row>
     <row r="107">
@@ -2355,11 +2355,11 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>PONTO</t>
+          <t>COTAPARACO</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>266</v>
+        <v>49</v>
       </c>
     </row>
     <row r="108">
@@ -2373,11 +2373,11 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>RAHUAPAMPA</t>
+          <t>PONTO</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>58</v>
+        <v>327</v>
       </c>
     </row>
     <row r="109">
@@ -2391,11 +2391,11 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>SAN MARCOS</t>
+          <t>RAHUAPAMPA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>3151</v>
+        <v>99</v>
       </c>
     </row>
     <row r="110">
@@ -2404,16 +2404,16 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>ANCASH</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>CHAPARRA</t>
+          <t>SAN MARCOS</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>151</v>
+        <v>3539</v>
       </c>
     </row>
     <row r="111">
@@ -2427,11 +2427,11 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>MARIANO NICOLAS VALCARCEL</t>
+          <t>CHAPARRA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>343</v>
+        <v>151</v>
       </c>
     </row>
     <row r="112">
@@ -2445,11 +2445,11 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>MOLLEBAYA</t>
+          <t>MARIANO NICOLAS VALCARCEL</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>220</v>
+        <v>365</v>
       </c>
     </row>
     <row r="113">
@@ -2463,11 +2463,11 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>QUEQUEÑA</t>
+          <t>MOLLEBAYA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>343</v>
+        <v>331</v>
       </c>
     </row>
     <row r="114">
@@ -2481,11 +2481,11 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>YARABAMBA</t>
+          <t>QUEQUEÑA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>419</v>
+        <v>343</v>
       </c>
     </row>
     <row r="115">
@@ -2494,16 +2494,16 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>AYACUCHO</t>
+          <t>AREQUIPA</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>COLTA</t>
+          <t>YARABAMBA</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>90</v>
+        <v>455</v>
       </c>
     </row>
     <row r="116">
@@ -2517,11 +2517,11 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>HUAC-HUAS</t>
+          <t>COLTA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>145</v>
+        <v>90</v>
       </c>
     </row>
     <row r="117">
@@ -2535,11 +2535,11 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>HUANCARAYLLA</t>
+          <t>HUAC-HUAS</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>219</v>
+        <v>145</v>
       </c>
     </row>
     <row r="118">
@@ -2548,16 +2548,16 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>CAJAMARCA</t>
+          <t>AYACUCHO</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>ANDABAMBA</t>
+          <t>HUANCARAYLLA</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>17</v>
+        <v>219</v>
       </c>
     </row>
     <row r="119">
@@ -2566,16 +2566,16 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>CUSCO</t>
+          <t>CAJAMARCA</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>PICHARI</t>
+          <t>ANDABAMBA</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>1176</v>
+        <v>17</v>
       </c>
     </row>
     <row r="120">
@@ -2589,11 +2589,11 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>SAYLLA</t>
+          <t>PICHARI</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>297</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="121">
@@ -2602,16 +2602,16 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>HUANCAVELICA</t>
+          <t>CUSCO</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>HUAYACUNDO ARMA</t>
+          <t>SAYLLA</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>61</v>
+        <v>297</v>
       </c>
     </row>
     <row r="122">
@@ -2625,11 +2625,11 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>PILCHACA</t>
+          <t>HUAYACUNDO ARMA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>27</v>
+        <v>61</v>
       </c>
     </row>
     <row r="123">
@@ -2643,11 +2643,11 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>TAMBO</t>
+          <t>PILCHACA</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>201</v>
+        <v>27</v>
       </c>
     </row>
     <row r="124">
@@ -2656,16 +2656,16 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>HUANUCO</t>
+          <t>HUANCAVELICA</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>CAHUAC</t>
+          <t>TAMBO</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>151</v>
+        <v>201</v>
       </c>
     </row>
     <row r="125">
@@ -2679,11 +2679,11 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>CASTILLO GRANDE</t>
+          <t>CAHUAC</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>808</v>
+        <v>151</v>
       </c>
     </row>
     <row r="126">
@@ -2697,11 +2697,11 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>CHACABAMBA</t>
+          <t>CASTILLO GRANDE</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>280</v>
+        <v>809</v>
       </c>
     </row>
     <row r="127">
@@ -2715,11 +2715,11 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>LA MORADA</t>
+          <t>CHACABAMBA</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>175</v>
+        <v>320</v>
       </c>
     </row>
     <row r="128">
@@ -2733,11 +2733,11 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>PAMPAMARCA</t>
+          <t>LA MORADA</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>166</v>
+        <v>176</v>
       </c>
     </row>
     <row r="129">
@@ -2751,11 +2751,11 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>SANTA ROSA DE ALTO YANAJANCA</t>
+          <t>PAMPAMARCA</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>71</v>
+        <v>166</v>
       </c>
     </row>
     <row r="130">
@@ -2769,11 +2769,11 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>YARUMAYO</t>
+          <t>SANTA ROSA DE ALTO YANAJANCA</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>201</v>
+        <v>72</v>
       </c>
     </row>
     <row r="131">
@@ -2782,16 +2782,16 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>HUANUCO</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>MARCAPOMACOCHA</t>
+          <t>YARUMAYO</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>214</v>
+        <v>201</v>
       </c>
     </row>
     <row r="132">
@@ -2805,11 +2805,11 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>VIZCATAN DEL ENE</t>
+          <t>MARCAPOMACOCHA</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>566</v>
+        <v>214</v>
       </c>
     </row>
     <row r="133">
@@ -2818,16 +2818,16 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>LIMA</t>
+          <t>JUNIN</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>ALIS</t>
+          <t>VIZCATAN DEL ENE</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>76</v>
+        <v>570</v>
       </c>
     </row>
     <row r="134">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>ALLAUCA</t>
+          <t>ALIS</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>106</v>
+        <v>76</v>
       </c>
     </row>
     <row r="135">
@@ -2859,11 +2859,11 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>AZANGARO</t>
+          <t>ALLAUCA</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>75</v>
+        <v>106</v>
       </c>
     </row>
     <row r="136">
@@ -2877,11 +2877,11 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>CARANIA</t>
+          <t>AZANGARO</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>20</v>
+        <v>75</v>
       </c>
     </row>
     <row r="137">
@@ -2895,11 +2895,11 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>HUAMPARA</t>
+          <t>CARANIA</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="138">
@@ -2913,11 +2913,11 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>HUANGASCAR</t>
+          <t>HUAMPARA</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>144</v>
+        <v>17</v>
       </c>
     </row>
     <row r="139">
@@ -2931,11 +2931,11 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>LARAOS</t>
+          <t>HUANGASCAR</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>113</v>
+        <v>144</v>
       </c>
     </row>
     <row r="140">
@@ -2949,11 +2949,11 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>PUTINZA</t>
+          <t>LARAOS</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>22</v>
+        <v>113</v>
       </c>
     </row>
     <row r="141">
@@ -2967,11 +2967,11 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>TOMAS</t>
+          <t>PUTINZA</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
     </row>
     <row r="142">
@@ -2980,16 +2980,16 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>LORETO</t>
+          <t>LIMA</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>SOPLIN</t>
+          <t>TOMAS</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>160</v>
+        <v>42</v>
       </c>
     </row>
     <row r="143">
@@ -3003,11 +3003,11 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>TAPICHE</t>
+          <t>SOPLIN</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>58</v>
+        <v>160</v>
       </c>
     </row>
     <row r="144">
@@ -3016,16 +3016,16 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>LORETO</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>TAHUAMANU</t>
+          <t>TAPICHE</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>105</v>
+        <v>84</v>
       </c>
     </row>
     <row r="145">
@@ -3034,16 +3034,16 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MOQUEGUA</t>
+          <t>MADRE DE DIOS</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>EL ALGARROBAL</t>
+          <t>TAHUAMANU</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>502</v>
+        <v>105</v>
       </c>
     </row>
     <row r="146">
@@ -3052,16 +3052,16 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>PASCO</t>
+          <t>MOQUEGUA</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>CHACAYAN</t>
+          <t>EL ALGARROBAL</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>196</v>
+        <v>517</v>
       </c>
     </row>
     <row r="147">
@@ -3075,11 +3075,11 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>GOYLLARISQUIZGA</t>
+          <t>CHACAYAN</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>29</v>
+        <v>196</v>
       </c>
     </row>
     <row r="148">
@@ -3088,16 +3088,16 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>PUNO</t>
+          <t>PASCO</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>LIMBANI</t>
+          <t>GOYLLARISQUIZGA</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>292</v>
+        <v>29</v>
       </c>
     </row>
     <row r="149">
@@ -3106,16 +3106,16 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>SAN MARTIN</t>
+          <t>PUNO</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>SHUNTE</t>
+          <t>LIMBANI</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>149</v>
+        <v>293</v>
       </c>
     </row>
     <row r="150">
@@ -3124,16 +3124,16 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>TACNA</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>HEROES ALBARRACIN</t>
+          <t>SHUNTE</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>83</v>
+        <v>149</v>
       </c>
     </row>
     <row r="151">
@@ -3147,11 +3147,11 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>ILABAYA</t>
+          <t>HEROES ALBARRACIN</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>575</v>
+        <v>83</v>
       </c>
     </row>
     <row r="152">
@@ -3165,29 +3165,29 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>SAMA</t>
+          <t>ILABAYA</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>147</v>
+        <v>630</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="n">
-        <v>46096</v>
+        <v>46095</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>AMAZONAS</t>
+          <t>TACNA</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>QUINJALCA</t>
+          <t>SAMA</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>46</v>
+        <v>153</v>
       </c>
     </row>
     <row r="154">
@@ -3201,11 +3201,11 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>SONCHE</t>
+          <t>QUINJALCA</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
     </row>
     <row r="155">
@@ -3214,16 +3214,16 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>ANCASH</t>
+          <t>AMAZONAS</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>ANRA</t>
+          <t>SONCHE</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>125</v>
+        <v>23</v>
       </c>
     </row>
     <row r="156">
@@ -3237,11 +3237,11 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>CHAVIN DE HUANTAR</t>
+          <t>ANRA</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>1428</v>
+        <v>200</v>
       </c>
     </row>
     <row r="157">
@@ -3255,11 +3255,11 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>COTAPARACO</t>
+          <t>CHAVIN DE HUANTAR</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>17</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="158">
@@ -3273,11 +3273,11 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>PONTO</t>
+          <t>COTAPARACO</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>481</v>
+        <v>17</v>
       </c>
     </row>
     <row r="159">
@@ -3291,11 +3291,11 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>RAHUAPAMPA</t>
+          <t>PONTO</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>114</v>
+        <v>528</v>
       </c>
     </row>
     <row r="160">
@@ -3309,11 +3309,11 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>SAN MARCOS</t>
+          <t>RAHUAPAMPA</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>2239</v>
+        <v>114</v>
       </c>
     </row>
     <row r="161">
@@ -3322,16 +3322,16 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>ANCASH</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>CHAPARRA</t>
+          <t>SAN CRISTOBAL DE RAJAN</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>137</v>
+        <v>1</v>
       </c>
     </row>
     <row r="162">
@@ -3340,16 +3340,16 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>ANCASH</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>MARIANO NICOLAS VALCARCEL</t>
+          <t>SAN MARCOS</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>146</v>
+        <v>2483</v>
       </c>
     </row>
     <row r="163">
@@ -3363,11 +3363,11 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>MOLLEBAYA</t>
+          <t>CHAPARRA</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>132</v>
+        <v>138</v>
       </c>
     </row>
     <row r="164">
@@ -3381,11 +3381,11 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>QUEQUEÑA</t>
+          <t>MARIANO NICOLAS VALCARCEL</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>238</v>
+        <v>412</v>
       </c>
     </row>
     <row r="165">
@@ -3399,11 +3399,11 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>YARABAMBA</t>
+          <t>MOLLEBAYA</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>265</v>
+        <v>175</v>
       </c>
     </row>
     <row r="166">
@@ -3412,16 +3412,16 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>AYACUCHO</t>
+          <t>AREQUIPA</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>COLTA</t>
+          <t>QUEQUEÑA</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>6</v>
+        <v>268</v>
       </c>
     </row>
     <row r="167">
@@ -3430,16 +3430,16 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>AYACUCHO</t>
+          <t>AREQUIPA</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>HUAC-HUAS</t>
+          <t>YARABAMBA</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>150</v>
+        <v>371</v>
       </c>
     </row>
     <row r="168">
@@ -3453,11 +3453,11 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>HUANCARAYLLA</t>
+          <t>COLTA</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>215</v>
+        <v>19</v>
       </c>
     </row>
     <row r="169">
@@ -3466,16 +3466,16 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>CUSCO</t>
+          <t>AYACUCHO</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>PICHARI</t>
+          <t>HUAC-HUAS</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>894</v>
+        <v>150</v>
       </c>
     </row>
     <row r="170">
@@ -3484,16 +3484,16 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>CUSCO</t>
+          <t>AYACUCHO</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>SAYLLA</t>
+          <t>HUANCARAYLLA</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>300</v>
+        <v>230</v>
       </c>
     </row>
     <row r="171">
@@ -3502,16 +3502,16 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>HUANCAVELICA</t>
+          <t>CUSCO</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>HUAYACUNDO ARMA</t>
+          <t>PICHARI</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>28</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="172">
@@ -3520,16 +3520,16 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>HUANCAVELICA</t>
+          <t>CUSCO</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>PILCHACA</t>
+          <t>SAYLLA</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>266</v>
+        <v>387</v>
       </c>
     </row>
     <row r="173">
@@ -3543,11 +3543,11 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>TAMBO</t>
+          <t>HUAYACUNDO ARMA</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>49</v>
+        <v>28</v>
       </c>
     </row>
     <row r="174">
@@ -3556,16 +3556,16 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>HUANUCO</t>
+          <t>HUANCAVELICA</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>CAHUAC</t>
+          <t>PILCHACA</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>61</v>
+        <v>272</v>
       </c>
     </row>
     <row r="175">
@@ -3574,16 +3574,16 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>HUANUCO</t>
+          <t>HUANCAVELICA</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>CASTILLO GRANDE</t>
+          <t>TAMBO</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>852</v>
+        <v>60</v>
       </c>
     </row>
     <row r="176">
@@ -3597,11 +3597,11 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>CHACABAMBA</t>
+          <t>CAHUAC</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>279</v>
+        <v>62</v>
       </c>
     </row>
     <row r="177">
@@ -3615,11 +3615,11 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>LA MORADA</t>
+          <t>CASTILLO GRANDE</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>151</v>
+        <v>876</v>
       </c>
     </row>
     <row r="178">
@@ -3633,11 +3633,11 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>PAMPAMARCA</t>
+          <t>CHACABAMBA</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>331</v>
+        <v>339</v>
       </c>
     </row>
     <row r="179">
@@ -3651,11 +3651,11 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>SANTA ROSA DE ALTO YANAJANCA</t>
+          <t>LA MORADA</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>50</v>
+        <v>151</v>
       </c>
     </row>
     <row r="180">
@@ -3669,11 +3669,11 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>YARUMAYO</t>
+          <t>PAMPAMARCA</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>215</v>
+        <v>355</v>
       </c>
     </row>
     <row r="181">
@@ -3682,16 +3682,16 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>HUANUCO</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>MARCAPOMACOCHA</t>
+          <t>SANTA ROSA DE ALTO YANAJANCA</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>209</v>
+        <v>70</v>
       </c>
     </row>
     <row r="182">
@@ -3700,16 +3700,16 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>HUANUCO</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>VIZCATAN DEL ENE</t>
+          <t>YARUMAYO</t>
         </is>
       </c>
       <c r="D182" t="n">
-        <v>139</v>
+        <v>252</v>
       </c>
     </row>
     <row r="183">
@@ -3718,16 +3718,16 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>LIMA</t>
+          <t>JUNIN</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>ALIS</t>
+          <t>MARCAPOMACOCHA</t>
         </is>
       </c>
       <c r="D183" t="n">
-        <v>7</v>
+        <v>209</v>
       </c>
     </row>
     <row r="184">
@@ -3736,16 +3736,16 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>LIMA</t>
+          <t>JUNIN</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>ALLAUCA</t>
+          <t>VIZCATAN DEL ENE</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>31</v>
+        <v>149</v>
       </c>
     </row>
     <row r="185">
@@ -3759,11 +3759,11 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>AZANGARO</t>
+          <t>ALIS</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="186">
@@ -3777,11 +3777,11 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>HUAMPARA</t>
+          <t>ALLAUCA</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>66</v>
+        <v>31</v>
       </c>
     </row>
     <row r="187">
@@ -3795,11 +3795,11 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>HUANGASCAR</t>
+          <t>AZANGARO</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>42</v>
+        <v>4</v>
       </c>
     </row>
     <row r="188">
@@ -3813,11 +3813,11 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>LARAOS</t>
+          <t>HUAMPARA</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>22</v>
+        <v>66</v>
       </c>
     </row>
     <row r="189">
@@ -3831,11 +3831,11 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>PUTINZA</t>
+          <t>HUANGASCAR</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>14</v>
+        <v>42</v>
       </c>
     </row>
     <row r="190">
@@ -3849,11 +3849,11 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>TOMAS</t>
+          <t>LARAOS</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>51</v>
+        <v>22</v>
       </c>
     </row>
     <row r="191">
@@ -3862,16 +3862,16 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>LORETO</t>
+          <t>LIMA</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>SOPLIN</t>
+          <t>PUTINZA</t>
         </is>
       </c>
       <c r="D191" t="n">
-        <v>90</v>
+        <v>27</v>
       </c>
     </row>
     <row r="192">
@@ -3880,16 +3880,16 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>LORETO</t>
+          <t>LIMA</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>TAPICHE</t>
+          <t>TOMAS</t>
         </is>
       </c>
       <c r="D192" t="n">
-        <v>23</v>
+        <v>53</v>
       </c>
     </row>
     <row r="193">
@@ -3898,16 +3898,16 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>LORETO</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>TAHUAMANU</t>
+          <t>SOPLIN</t>
         </is>
       </c>
       <c r="D193" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
     </row>
     <row r="194">
@@ -3916,16 +3916,16 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>MOQUEGUA</t>
+          <t>LORETO</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>EL ALGARROBAL</t>
+          <t>TAPICHE</t>
         </is>
       </c>
       <c r="D194" t="n">
-        <v>374</v>
+        <v>24</v>
       </c>
     </row>
     <row r="195">
@@ -3934,16 +3934,16 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>PASCO</t>
+          <t>MADRE DE DIOS</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>CHACAYAN</t>
+          <t>TAHUAMANU</t>
         </is>
       </c>
       <c r="D195" t="n">
-        <v>201</v>
+        <v>35</v>
       </c>
     </row>
     <row r="196">
@@ -3952,16 +3952,16 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>PASCO</t>
+          <t>MOQUEGUA</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>GOYLLARISQUIZGA</t>
+          <t>EL ALGARROBAL</t>
         </is>
       </c>
       <c r="D196" t="n">
-        <v>91</v>
+        <v>415</v>
       </c>
     </row>
     <row r="197">
@@ -3970,16 +3970,16 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>PUNO</t>
+          <t>PASCO</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>LIMBANI</t>
+          <t>CHACAYAN</t>
         </is>
       </c>
       <c r="D197" t="n">
-        <v>391</v>
+        <v>201</v>
       </c>
     </row>
     <row r="198">
@@ -3988,16 +3988,16 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>SAN MARTIN</t>
+          <t>PASCO</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>SHUNTE</t>
+          <t>GOYLLARISQUIZGA</t>
         </is>
       </c>
       <c r="D198" t="n">
-        <v>54</v>
+        <v>91</v>
       </c>
     </row>
     <row r="199">
@@ -4006,16 +4006,16 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>TACNA</t>
+          <t>PUNO</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>HEROES ALBARRACIN</t>
+          <t>LIMBANI</t>
         </is>
       </c>
       <c r="D199" t="n">
-        <v>119</v>
+        <v>393</v>
       </c>
     </row>
     <row r="200">
@@ -4024,16 +4024,16 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>TACNA</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>ILABAYA</t>
+          <t>SHUNTE</t>
         </is>
       </c>
       <c r="D200" t="n">
-        <v>533</v>
+        <v>197</v>
       </c>
     </row>
     <row r="201">
@@ -4047,47 +4047,47 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>SAMA</t>
+          <t>HEROES ALBARRACIN</t>
         </is>
       </c>
       <c r="D201" t="n">
-        <v>202</v>
+        <v>119</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="n">
-        <v>46097</v>
+        <v>46096</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>AMAZONAS</t>
+          <t>TACNA</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>SONCHE</t>
+          <t>ILABAYA</t>
         </is>
       </c>
       <c r="D202" t="n">
-        <v>9</v>
+        <v>590</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="n">
-        <v>46097</v>
+        <v>46096</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>ANCASH</t>
+          <t>TACNA</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>ANRA</t>
+          <t>SAMA</t>
         </is>
       </c>
       <c r="D203" t="n">
-        <v>43</v>
+        <v>215</v>
       </c>
     </row>
     <row r="204">
@@ -4096,12 +4096,12 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>ANCASH</t>
+          <t>AMAZONAS</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>CHAVIN DE HUANTAR</t>
+          <t>SONCHE</t>
         </is>
       </c>
       <c r="D204" t="n">
@@ -4119,11 +4119,11 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>PONTO</t>
+          <t>ANRA</t>
         </is>
       </c>
       <c r="D205" t="n">
-        <v>20</v>
+        <v>234</v>
       </c>
     </row>
     <row r="206">
@@ -4137,11 +4137,11 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>SAN MARCOS</t>
+          <t>CHAVIN DE HUANTAR</t>
         </is>
       </c>
       <c r="D206" t="n">
-        <v>617</v>
+        <v>32</v>
       </c>
     </row>
     <row r="207">
@@ -4150,16 +4150,16 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>ANCASH</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>CHAPARRA</t>
+          <t>COTAPARACO</t>
         </is>
       </c>
       <c r="D207" t="n">
-        <v>49</v>
+        <v>18</v>
       </c>
     </row>
     <row r="208">
@@ -4168,16 +4168,16 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>ANCASH</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>MARIANO NICOLAS VALCARCEL</t>
+          <t>PONTO</t>
         </is>
       </c>
       <c r="D208" t="n">
-        <v>29</v>
+        <v>231</v>
       </c>
     </row>
     <row r="209">
@@ -4186,16 +4186,16 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>ANCASH</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>MOLLEBAYA</t>
+          <t>SAN MARCOS</t>
         </is>
       </c>
       <c r="D209" t="n">
-        <v>75</v>
+        <v>949</v>
       </c>
     </row>
     <row r="210">
@@ -4209,11 +4209,11 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>QUEQUEÑA</t>
+          <t>CHAPARRA</t>
         </is>
       </c>
       <c r="D210" t="n">
-        <v>89</v>
+        <v>67</v>
       </c>
     </row>
     <row r="211">
@@ -4227,11 +4227,11 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>YARABAMBA</t>
+          <t>MARIANO NICOLAS VALCARCEL</t>
         </is>
       </c>
       <c r="D211" t="n">
-        <v>90</v>
+        <v>132</v>
       </c>
     </row>
     <row r="212">
@@ -4240,16 +4240,16 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>AYACUCHO</t>
+          <t>AREQUIPA</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>HUAC-HUAS</t>
+          <t>MOLLEBAYA</t>
         </is>
       </c>
       <c r="D212" t="n">
-        <v>70</v>
+        <v>119</v>
       </c>
     </row>
     <row r="213">
@@ -4258,16 +4258,16 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>AYACUCHO</t>
+          <t>AREQUIPA</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>HUANCARAYLLA</t>
+          <t>QUEQUEÑA</t>
         </is>
       </c>
       <c r="D213" t="n">
-        <v>29</v>
+        <v>161</v>
       </c>
     </row>
     <row r="214">
@@ -4276,16 +4276,16 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>CUSCO</t>
+          <t>AREQUIPA</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>PICHARI</t>
+          <t>YARABAMBA</t>
         </is>
       </c>
       <c r="D214" t="n">
-        <v>488</v>
+        <v>464</v>
       </c>
     </row>
     <row r="215">
@@ -4294,16 +4294,16 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>CUSCO</t>
+          <t>AYACUCHO</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>SAYLLA</t>
+          <t>COLTA</t>
         </is>
       </c>
       <c r="D215" t="n">
-        <v>202</v>
+        <v>14</v>
       </c>
     </row>
     <row r="216">
@@ -4312,16 +4312,16 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>HUANCAVELICA</t>
+          <t>AYACUCHO</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>HUAYACUNDO ARMA</t>
+          <t>HUAC-HUAS</t>
         </is>
       </c>
       <c r="D216" t="n">
-        <v>17</v>
+        <v>152</v>
       </c>
     </row>
     <row r="217">
@@ -4330,16 +4330,16 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>HUANCAVELICA</t>
+          <t>AYACUCHO</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>PILCHACA</t>
+          <t>HUANCARAYLLA</t>
         </is>
       </c>
       <c r="D217" t="n">
-        <v>22</v>
+        <v>49</v>
       </c>
     </row>
     <row r="218">
@@ -4348,16 +4348,16 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>HUANCAVELICA</t>
+          <t>CUSCO</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>TAMBO</t>
+          <t>PICHARI</t>
         </is>
       </c>
       <c r="D218" t="n">
-        <v>4</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="219">
@@ -4366,16 +4366,16 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>HUANUCO</t>
+          <t>CUSCO</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>CAHUAC</t>
+          <t>SAYLLA</t>
         </is>
       </c>
       <c r="D219" t="n">
-        <v>9</v>
+        <v>318</v>
       </c>
     </row>
     <row r="220">
@@ -4384,16 +4384,16 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>HUANUCO</t>
+          <t>HUANCAVELICA</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>CASTILLO GRANDE</t>
+          <t>HUAYACUNDO ARMA</t>
         </is>
       </c>
       <c r="D220" t="n">
-        <v>94</v>
+        <v>35</v>
       </c>
     </row>
     <row r="221">
@@ -4402,16 +4402,16 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>HUANUCO</t>
+          <t>HUANCAVELICA</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>CHACABAMBA</t>
+          <t>PILCHACA</t>
         </is>
       </c>
       <c r="D221" t="n">
-        <v>29</v>
+        <v>41</v>
       </c>
     </row>
     <row r="222">
@@ -4420,16 +4420,16 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>HUANUCO</t>
+          <t>HUANCAVELICA</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>LA MORADA</t>
+          <t>TAMBO</t>
         </is>
       </c>
       <c r="D222" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
     </row>
     <row r="223">
@@ -4443,11 +4443,11 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>SANTA ROSA DE ALTO YANAJANCA</t>
+          <t>CAHUAC</t>
         </is>
       </c>
       <c r="D223" t="n">
-        <v>60</v>
+        <v>107</v>
       </c>
     </row>
     <row r="224">
@@ -4461,11 +4461,11 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>YARUMAYO</t>
+          <t>CASTILLO GRANDE</t>
         </is>
       </c>
       <c r="D224" t="n">
-        <v>1</v>
+        <v>141</v>
       </c>
     </row>
     <row r="225">
@@ -4474,16 +4474,16 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>HUANUCO</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>MARCAPOMACOCHA</t>
+          <t>CHACABAMBA</t>
         </is>
       </c>
       <c r="D225" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
     </row>
     <row r="226">
@@ -4492,16 +4492,16 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>LIMA</t>
+          <t>HUANUCO</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>ALLAUCA</t>
+          <t>LA MORADA</t>
         </is>
       </c>
       <c r="D226" t="n">
-        <v>31</v>
+        <v>198</v>
       </c>
     </row>
     <row r="227">
@@ -4510,16 +4510,16 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>LIMA</t>
+          <t>HUANUCO</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>HUAMPARA</t>
+          <t>SANTA ROSA DE ALTO YANAJANCA</t>
         </is>
       </c>
       <c r="D227" t="n">
-        <v>21</v>
+        <v>96</v>
       </c>
     </row>
     <row r="228">
@@ -4528,16 +4528,16 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>LIMA</t>
+          <t>HUANUCO</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>HUANGASCAR</t>
+          <t>YARUMAYO</t>
         </is>
       </c>
       <c r="D228" t="n">
-        <v>7</v>
+        <v>89</v>
       </c>
     </row>
     <row r="229">
@@ -4546,16 +4546,16 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>LIMA</t>
+          <t>JUNIN</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>PUTINZA</t>
+          <t>MARCAPOMACOCHA</t>
         </is>
       </c>
       <c r="D229" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="230">
@@ -4569,11 +4569,11 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>TOMAS</t>
+          <t>ALIS</t>
         </is>
       </c>
       <c r="D230" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="231">
@@ -4582,16 +4582,16 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>LORETO</t>
+          <t>LIMA</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>SOPLIN</t>
+          <t>ALLAUCA</t>
         </is>
       </c>
       <c r="D231" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
     </row>
     <row r="232">
@@ -4600,16 +4600,16 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>LIMA</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>TAHUAMANU</t>
+          <t>HUAMPARA</t>
         </is>
       </c>
       <c r="D232" t="n">
-        <v>32</v>
+        <v>86</v>
       </c>
     </row>
     <row r="233">
@@ -4618,16 +4618,16 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>MOQUEGUA</t>
+          <t>LIMA</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>EL ALGARROBAL</t>
+          <t>HUANGASCAR</t>
         </is>
       </c>
       <c r="D233" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
     </row>
     <row r="234">
@@ -4636,16 +4636,16 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>PASCO</t>
+          <t>LIMA</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>GOYLLARISQUIZGA</t>
+          <t>PUTINZA</t>
         </is>
       </c>
       <c r="D234" t="n">
-        <v>84</v>
+        <v>66</v>
       </c>
     </row>
     <row r="235">
@@ -4654,16 +4654,16 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>PUNO</t>
+          <t>LIMA</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>LIMBANI</t>
+          <t>TOMAS</t>
         </is>
       </c>
       <c r="D235" t="n">
-        <v>70</v>
+        <v>58</v>
       </c>
     </row>
     <row r="236">
@@ -4672,16 +4672,16 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>SAN MARTIN</t>
+          <t>LORETO</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>SHUNTE</t>
+          <t>SOPLIN</t>
         </is>
       </c>
       <c r="D236" t="n">
-        <v>48</v>
+        <v>2</v>
       </c>
     </row>
     <row r="237">
@@ -4690,16 +4690,16 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>TACNA</t>
+          <t>MADRE DE DIOS</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>HEROES ALBARRACIN</t>
+          <t>TAHUAMANU</t>
         </is>
       </c>
       <c r="D237" t="n">
-        <v>34</v>
+        <v>51</v>
       </c>
     </row>
     <row r="238">
@@ -4708,16 +4708,16 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>TACNA</t>
+          <t>MOQUEGUA</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>ILABAYA</t>
+          <t>EL ALGARROBAL</t>
         </is>
       </c>
       <c r="D238" t="n">
-        <v>50</v>
+        <v>22</v>
       </c>
     </row>
     <row r="239">
@@ -4726,70 +4726,520 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>TACNA</t>
+          <t>PASCO</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>SAMA</t>
+          <t>GOYLLARISQUIZGA</t>
         </is>
       </c>
       <c r="D239" t="n">
-        <v>69</v>
+        <v>87</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="n">
-        <v>46098</v>
+        <v>46097</v>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>ANCASH</t>
+          <t>PUNO</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>PONTO</t>
+          <t>LIMBANI</t>
         </is>
       </c>
       <c r="D240" t="n">
-        <v>1</v>
+        <v>355</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="n">
-        <v>46098</v>
+        <v>46097</v>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>ANCASH</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>SAN MARCOS</t>
+          <t>SHUNTE</t>
         </is>
       </c>
       <c r="D241" t="n">
-        <v>4</v>
+        <v>101</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>HEROES ALBARRACIN</t>
+        </is>
+      </c>
+      <c r="D242" t="n">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>ILABAYA</t>
+        </is>
+      </c>
+      <c r="D243" t="n">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>SAMA</t>
+        </is>
+      </c>
+      <c r="D244" t="n">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="2" t="n">
         <v>46098</v>
       </c>
-      <c r="B242" t="inlineStr">
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>ANRA</t>
+        </is>
+      </c>
+      <c r="D245" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>CHAVIN DE HUANTAR</t>
+        </is>
+      </c>
+      <c r="D246" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>PONTO</t>
+        </is>
+      </c>
+      <c r="D247" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>SAN MARCOS</t>
+        </is>
+      </c>
+      <c r="D248" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>MARIANO NICOLAS VALCARCEL</t>
+        </is>
+      </c>
+      <c r="D249" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>MOLLEBAYA</t>
+        </is>
+      </c>
+      <c r="D250" t="n">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>QUEQUEÑA</t>
+        </is>
+      </c>
+      <c r="D251" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>YARABAMBA</t>
+        </is>
+      </c>
+      <c r="D252" t="n">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>COLTA</t>
+        </is>
+      </c>
+      <c r="D253" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>HUAC-HUAS</t>
+        </is>
+      </c>
+      <c r="D254" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>CUSCO</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>PICHARI</t>
+        </is>
+      </c>
+      <c r="D255" t="n">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>CUSCO</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>SAYLLA</t>
+        </is>
+      </c>
+      <c r="D256" t="n">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>PILCHACA</t>
+        </is>
+      </c>
+      <c r="D257" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>LA MORADA</t>
+        </is>
+      </c>
+      <c r="D258" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>SANTA ROSA DE ALTO YANAJANCA</t>
+        </is>
+      </c>
+      <c r="D259" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>YARUMAYO</t>
+        </is>
+      </c>
+      <c r="D260" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>ALIS</t>
+        </is>
+      </c>
+      <c r="D261" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>TOMAS</t>
+        </is>
+      </c>
+      <c r="D262" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>TAHUAMANU</t>
+        </is>
+      </c>
+      <c r="D263" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B264" t="inlineStr">
         <is>
           <t>MOQUEGUA</t>
         </is>
       </c>
-      <c r="C242" t="inlineStr">
+      <c r="C264" t="inlineStr">
         <is>
           <t>EL ALGARROBAL</t>
         </is>
       </c>
-      <c r="D242" t="n">
+      <c r="D264" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>PASCO</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>GOYLLARISQUIZGA</t>
+        </is>
+      </c>
+      <c r="D265" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>ILABAYA</t>
+        </is>
+      </c>
+      <c r="D266" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>SAMA</t>
+        </is>
+      </c>
+      <c r="D267" t="n">
+        <v>127</v>
       </c>
     </row>
   </sheetData>

--- a/data/data_distritos.xlsx
+++ b/data/data_distritos.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D267"/>
+  <dimension ref="A1:D171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,7 +505,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="5">
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>610</v>
+        <v>544</v>
       </c>
     </row>
     <row r="6">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7">
@@ -559,7 +559,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>503</v>
+        <v>154</v>
       </c>
     </row>
     <row r="8">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>95</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9">
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1255</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="10">
@@ -613,7 +613,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>143</v>
+        <v>127</v>
       </c>
     </row>
     <row r="11">
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="12">
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13">
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>52</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14">
@@ -685,7 +685,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>54</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15">
@@ -775,7 +775,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>343</v>
+        <v>338</v>
       </c>
     </row>
     <row r="20">
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>93</v>
+        <v>85</v>
       </c>
     </row>
     <row r="25">
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>332</v>
+        <v>309</v>
       </c>
     </row>
     <row r="26">
@@ -901,7 +901,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>176</v>
+        <v>135</v>
       </c>
     </row>
     <row r="27">
@@ -919,7 +919,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>70</v>
+        <v>58</v>
       </c>
     </row>
     <row r="28">
@@ -933,11 +933,11 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>PAMPAMARCA</t>
+          <t>SANTA ROSA DE ALTO YANAJANCA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29">
@@ -951,11 +951,11 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>SANTA ROSA DE ALTO YANAJANCA</t>
+          <t>YARUMAYO</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>21</v>
+        <v>167</v>
       </c>
     </row>
     <row r="30">
@@ -964,16 +964,16 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>HUANUCO</t>
+          <t>JUNIN</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>YARUMAYO</t>
+          <t>MARCAPOMACOCHA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>178</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -987,11 +987,11 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>MARCAPOMACOCHA</t>
+          <t>VIZCATAN DEL ENE</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>68</v>
       </c>
     </row>
     <row r="32">
@@ -1000,16 +1000,16 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>LIMA</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>VIZCATAN DEL ENE</t>
+          <t>ALIS</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>152</v>
+        <v>19</v>
       </c>
     </row>
     <row r="33">
@@ -1023,11 +1023,11 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ALIS</t>
+          <t>ALLAUCA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>20</v>
+        <v>148</v>
       </c>
     </row>
     <row r="34">
@@ -1041,11 +1041,11 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ALLAUCA</t>
+          <t>AZANGARO</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>261</v>
+        <v>48</v>
       </c>
     </row>
     <row r="35">
@@ -1059,11 +1059,11 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>AZANGARO</t>
+          <t>CARANIA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>126</v>
+        <v>24</v>
       </c>
     </row>
     <row r="36">
@@ -1077,11 +1077,11 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CARANIA</t>
+          <t>HUAMPARA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -1095,11 +1095,11 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>HUAMPARA</t>
+          <t>HUANGASCAR</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
     </row>
     <row r="38">
@@ -1113,11 +1113,11 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>HUANGASCAR</t>
+          <t>LARAOS</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="39">
@@ -1131,11 +1131,11 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>LARAOS</t>
+          <t>PUTINZA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40">
@@ -1149,11 +1149,11 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>PUTINZA</t>
+          <t>TOMAS</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>16</v>
+        <v>34</v>
       </c>
     </row>
     <row r="41">
@@ -1162,16 +1162,16 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>LIMA</t>
+          <t>LORETO</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>TOMAS</t>
+          <t>SOPLIN</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="42">
@@ -1185,11 +1185,11 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>SOPLIN</t>
+          <t>TAPICHE</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>51</v>
+        <v>173</v>
       </c>
     </row>
     <row r="43">
@@ -1198,16 +1198,16 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>LORETO</t>
+          <t>MADRE DE DIOS</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>TAPICHE</t>
+          <t>TAHUAMANU</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>173</v>
+        <v>4</v>
       </c>
     </row>
     <row r="44">
@@ -1216,16 +1216,16 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>MOQUEGUA</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>TAHUAMANU</t>
+          <t>EL ALGARROBAL</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>4</v>
+        <v>252</v>
       </c>
     </row>
     <row r="45">
@@ -1234,16 +1234,16 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>MOQUEGUA</t>
+          <t>PASCO</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>EL ALGARROBAL</t>
+          <t>CHACAYAN</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>268</v>
+        <v>14</v>
       </c>
     </row>
     <row r="46">
@@ -1257,11 +1257,11 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>CHACAYAN</t>
+          <t>GOYLLARISQUIZGA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47">
@@ -1270,16 +1270,16 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>PASCO</t>
+          <t>PUNO</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>GOYLLARISQUIZGA</t>
+          <t>LIMBANI</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>3</v>
+        <v>77</v>
       </c>
     </row>
     <row r="48">
@@ -1288,16 +1288,16 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>PUNO</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>LIMBANI</t>
+          <t>SHUNTE</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>77</v>
+        <v>86</v>
       </c>
     </row>
     <row r="49">
@@ -1306,16 +1306,16 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SAN MARTIN</t>
+          <t>TACNA</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>SHUNTE</t>
+          <t>ILABAYA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>86</v>
+        <v>145</v>
       </c>
     </row>
     <row r="50">
@@ -1329,29 +1329,29 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ILABAYA</t>
+          <t>SAMA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>188</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>TACNA</t>
+          <t>AMAZONAS</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>SAMA</t>
+          <t>QUINJALCA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>18</v>
+        <v>38</v>
       </c>
     </row>
     <row r="52">
@@ -1365,11 +1365,11 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>QUINJALCA</t>
+          <t>SONCHE</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>38</v>
+        <v>13</v>
       </c>
     </row>
     <row r="53">
@@ -1378,16 +1378,16 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>AMAZONAS</t>
+          <t>ANCASH</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>SONCHE</t>
+          <t>ANRA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>13</v>
+        <v>200</v>
       </c>
     </row>
     <row r="54">
@@ -1401,11 +1401,11 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ANRA</t>
+          <t>CHAVIN DE HUANTAR</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>203</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="55">
@@ -1419,11 +1419,11 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>CHAVIN DE HUANTAR</t>
+          <t>COTAPARACO</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1881</v>
+        <v>31</v>
       </c>
     </row>
     <row r="56">
@@ -1437,11 +1437,11 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>COTAPARACO</t>
+          <t>PONTO</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>31</v>
+        <v>244</v>
       </c>
     </row>
     <row r="57">
@@ -1455,11 +1455,11 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>PONTO</t>
+          <t>RAHUAPAMPA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>468</v>
+        <v>70</v>
       </c>
     </row>
     <row r="58">
@@ -1473,11 +1473,11 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>RAHUAPAMPA</t>
+          <t>SAN MARCOS</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>157</v>
+        <v>2541</v>
       </c>
     </row>
     <row r="59">
@@ -1486,16 +1486,16 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ANCASH</t>
+          <t>AREQUIPA</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>SAN MARCOS</t>
+          <t>CHAPARRA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>3511</v>
+        <v>188</v>
       </c>
     </row>
     <row r="60">
@@ -1509,11 +1509,11 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>CHAPARRA</t>
+          <t>MARIANO NICOLAS VALCARCEL</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>231</v>
+        <v>390</v>
       </c>
     </row>
     <row r="61">
@@ -1527,11 +1527,11 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>MARIANO NICOLAS VALCARCEL</t>
+          <t>MOLLEBAYA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>437</v>
+        <v>68</v>
       </c>
     </row>
     <row r="62">
@@ -1545,11 +1545,11 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>MOLLEBAYA</t>
+          <t>QUEQUEÑA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>105</v>
+        <v>152</v>
       </c>
     </row>
     <row r="63">
@@ -1563,11 +1563,11 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>QUEQUEÑA</t>
+          <t>YARABAMBA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>167</v>
+        <v>155</v>
       </c>
     </row>
     <row r="64">
@@ -1576,16 +1576,16 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>AYACUCHO</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>YARABAMBA</t>
+          <t>COLTA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>208</v>
+        <v>101</v>
       </c>
     </row>
     <row r="65">
@@ -1599,11 +1599,11 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>COLTA</t>
+          <t>HUAC-HUAS</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>102</v>
+        <v>75</v>
       </c>
     </row>
     <row r="66">
@@ -1617,11 +1617,11 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>HUAC-HUAS</t>
+          <t>HUANCARAYLLA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>75</v>
+        <v>175</v>
       </c>
     </row>
     <row r="67">
@@ -1630,16 +1630,16 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>AYACUCHO</t>
+          <t>CAJAMARCA</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>HUANCARAYLLA</t>
+          <t>ANDABAMBA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>175</v>
+        <v>11</v>
       </c>
     </row>
     <row r="68">
@@ -1648,16 +1648,16 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>CAJAMARCA</t>
+          <t>CUSCO</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>ANDABAMBA</t>
+          <t>PICHARI</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>29</v>
+        <v>971</v>
       </c>
     </row>
     <row r="69">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>PICHARI</t>
+          <t>SAYLLA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1002</v>
+        <v>233</v>
       </c>
     </row>
     <row r="70">
@@ -1684,16 +1684,16 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>CUSCO</t>
+          <t>HUANCAVELICA</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>SAYLLA</t>
+          <t>HUAYACUNDO ARMA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>233</v>
+        <v>39</v>
       </c>
     </row>
     <row r="71">
@@ -1707,11 +1707,11 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>HUAYACUNDO ARMA</t>
+          <t>PILCHACA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>39</v>
+        <v>12</v>
       </c>
     </row>
     <row r="72">
@@ -1725,11 +1725,11 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>PILCHACA</t>
+          <t>TAMBO</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>19</v>
+        <v>82</v>
       </c>
     </row>
     <row r="73">
@@ -1738,16 +1738,16 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>HUANCAVELICA</t>
+          <t>HUANUCO</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>TAMBO</t>
+          <t>CAHUAC</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>82</v>
+        <v>117</v>
       </c>
     </row>
     <row r="74">
@@ -1761,11 +1761,11 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>CAHUAC</t>
+          <t>CASTILLO GRANDE</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>139</v>
+        <v>185</v>
       </c>
     </row>
     <row r="75">
@@ -1779,11 +1779,11 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>CASTILLO GRANDE</t>
+          <t>CHACABAMBA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>195</v>
+        <v>166</v>
       </c>
     </row>
     <row r="76">
@@ -1797,11 +1797,11 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>CHACABAMBA</t>
+          <t>LA MORADA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>253</v>
+        <v>134</v>
       </c>
     </row>
     <row r="77">
@@ -1815,11 +1815,11 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>LA MORADA</t>
+          <t>PAMPAMARCA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>153</v>
+        <v>189</v>
       </c>
     </row>
     <row r="78">
@@ -1833,11 +1833,11 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>PAMPAMARCA</t>
+          <t>SANTA ROSA DE ALTO YANAJANCA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>189</v>
+        <v>13</v>
       </c>
     </row>
     <row r="79">
@@ -1851,11 +1851,11 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>SANTA ROSA DE ALTO YANAJANCA</t>
+          <t>YARUMAYO</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>14</v>
+        <v>191</v>
       </c>
     </row>
     <row r="80">
@@ -1864,16 +1864,16 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>HUANUCO</t>
+          <t>JUNIN</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>YARUMAYO</t>
+          <t>MARCAPOMACOCHA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>218</v>
+        <v>26</v>
       </c>
     </row>
     <row r="81">
@@ -1887,11 +1887,11 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>MARCAPOMACOCHA</t>
+          <t>VIZCATAN DEL ENE</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>26</v>
+        <v>414</v>
       </c>
     </row>
     <row r="82">
@@ -1900,16 +1900,16 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>LIMA</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>VIZCATAN DEL ENE</t>
+          <t>ALIS</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>534</v>
+        <v>78</v>
       </c>
     </row>
     <row r="83">
@@ -1923,11 +1923,11 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>ALIS</t>
+          <t>ALLAUCA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>80</v>
+        <v>18</v>
       </c>
     </row>
     <row r="84">
@@ -1941,11 +1941,11 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>ALLAUCA</t>
+          <t>CARANIA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>127</v>
+        <v>30</v>
       </c>
     </row>
     <row r="85">
@@ -1959,11 +1959,11 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>AZANGARO</t>
+          <t>HUAMPARA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
     </row>
     <row r="86">
@@ -1977,11 +1977,11 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>CARANIA</t>
+          <t>HUANGASCAR</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>30</v>
+        <v>85</v>
       </c>
     </row>
     <row r="87">
@@ -1995,11 +1995,11 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>HUAMPARA</t>
+          <t>LARAOS</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>71</v>
+        <v>36</v>
       </c>
     </row>
     <row r="88">
@@ -2013,11 +2013,11 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>HUANGASCAR</t>
+          <t>PUTINZA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>85</v>
+        <v>5</v>
       </c>
     </row>
     <row r="89">
@@ -2031,11 +2031,11 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>LARAOS</t>
+          <t>TOMAS</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="90">
@@ -2044,16 +2044,16 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>LIMA</t>
+          <t>LORETO</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>PUTINZA</t>
+          <t>SOPLIN</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
@@ -2062,16 +2062,16 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>LIMA</t>
+          <t>LORETO</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>TOMAS</t>
+          <t>TAPICHE</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>34</v>
+        <v>165</v>
       </c>
     </row>
     <row r="92">
@@ -2080,16 +2080,16 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>LORETO</t>
+          <t>MADRE DE DIOS</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>SOPLIN</t>
+          <t>TAHUAMANU</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>1</v>
+        <v>70</v>
       </c>
     </row>
     <row r="93">
@@ -2098,16 +2098,16 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>LORETO</t>
+          <t>MOQUEGUA</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>TAPICHE</t>
+          <t>EL ALGARROBAL</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>287</v>
+        <v>507</v>
       </c>
     </row>
     <row r="94">
@@ -2116,16 +2116,16 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>PASCO</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>TAHUAMANU</t>
+          <t>CHACAYAN</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>70</v>
+        <v>102</v>
       </c>
     </row>
     <row r="95">
@@ -2134,16 +2134,16 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>MOQUEGUA</t>
+          <t>PASCO</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>EL ALGARROBAL</t>
+          <t>GOYLLARISQUIZGA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>632</v>
+        <v>23</v>
       </c>
     </row>
     <row r="96">
@@ -2152,16 +2152,16 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>PASCO</t>
+          <t>PUNO</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>CHACAYAN</t>
+          <t>LIMBANI</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>102</v>
+        <v>175</v>
       </c>
     </row>
     <row r="97">
@@ -2170,16 +2170,16 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>PASCO</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>GOYLLARISQUIZGA</t>
+          <t>SHUNTE</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>23</v>
+        <v>204</v>
       </c>
     </row>
     <row r="98">
@@ -2188,16 +2188,16 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>PUNO</t>
+          <t>TACNA</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>LIMBANI</t>
+          <t>HEROES ALBARRACIN</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>175</v>
+        <v>135</v>
       </c>
     </row>
     <row r="99">
@@ -2206,16 +2206,16 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>SAN MARTIN</t>
+          <t>TACNA</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>SHUNTE</t>
+          <t>ILABAYA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>204</v>
+        <v>309</v>
       </c>
     </row>
     <row r="100">
@@ -2229,47 +2229,47 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>HEROES ALBARRACIN</t>
+          <t>SAMA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>135</v>
+        <v>60</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>46094</v>
+        <v>46095</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>TACNA</t>
+          <t>AMAZONAS</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>ILABAYA</t>
+          <t>QUINJALCA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>563</v>
+        <v>76</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>46094</v>
+        <v>46095</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>TACNA</t>
+          <t>AMAZONAS</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>SAMA</t>
+          <t>SONCHE</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>117</v>
+        <v>23</v>
       </c>
     </row>
     <row r="103">
@@ -2278,16 +2278,16 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>AMAZONAS</t>
+          <t>ANCASH</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>QUINJALCA</t>
+          <t>ANRA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>76</v>
+        <v>100</v>
       </c>
     </row>
     <row r="104">
@@ -2296,16 +2296,16 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>AMAZONAS</t>
+          <t>ANCASH</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>SONCHE</t>
+          <t>CHAVIN DE HUANTAR</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>25</v>
+        <v>544</v>
       </c>
     </row>
     <row r="105">
@@ -2319,11 +2319,11 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>ANRA</t>
+          <t>COTAPARACO</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>246</v>
+        <v>49</v>
       </c>
     </row>
     <row r="106">
@@ -2337,11 +2337,11 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>CHAVIN DE HUANTAR</t>
+          <t>PONTO</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>2212</v>
+        <v>30</v>
       </c>
     </row>
     <row r="107">
@@ -2355,11 +2355,11 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>COTAPARACO</t>
+          <t>RAHUAPAMPA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>49</v>
+        <v>21</v>
       </c>
     </row>
     <row r="108">
@@ -2373,11 +2373,11 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>PONTO</t>
+          <t>SAN MARCOS</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>327</v>
+        <v>991</v>
       </c>
     </row>
     <row r="109">
@@ -2386,16 +2386,16 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>ANCASH</t>
+          <t>AREQUIPA</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>RAHUAPAMPA</t>
+          <t>CHAPARRA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>99</v>
+        <v>47</v>
       </c>
     </row>
     <row r="110">
@@ -2404,16 +2404,16 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>ANCASH</t>
+          <t>AREQUIPA</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>SAN MARCOS</t>
+          <t>MARIANO NICOLAS VALCARCEL</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>3539</v>
+        <v>63</v>
       </c>
     </row>
     <row r="111">
@@ -2427,11 +2427,11 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>CHAPARRA</t>
+          <t>MOLLEBAYA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>151</v>
+        <v>157</v>
       </c>
     </row>
     <row r="112">
@@ -2445,11 +2445,11 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>MARIANO NICOLAS VALCARCEL</t>
+          <t>QUEQUEÑA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>365</v>
+        <v>321</v>
       </c>
     </row>
     <row r="113">
@@ -2463,11 +2463,11 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>MOLLEBAYA</t>
+          <t>YARABAMBA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>331</v>
+        <v>264</v>
       </c>
     </row>
     <row r="114">
@@ -2476,16 +2476,16 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>AYACUCHO</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>QUEQUEÑA</t>
+          <t>COLTA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>343</v>
+        <v>50</v>
       </c>
     </row>
     <row r="115">
@@ -2494,16 +2494,16 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>AYACUCHO</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>YARABAMBA</t>
+          <t>HUAC-HUAS</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>455</v>
+        <v>125</v>
       </c>
     </row>
     <row r="116">
@@ -2517,11 +2517,11 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>COLTA</t>
+          <t>HUANCARAYLLA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>90</v>
+        <v>136</v>
       </c>
     </row>
     <row r="117">
@@ -2530,16 +2530,16 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>AYACUCHO</t>
+          <t>CAJAMARCA</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>HUAC-HUAS</t>
+          <t>ANDABAMBA</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>145</v>
+        <v>3</v>
       </c>
     </row>
     <row r="118">
@@ -2548,16 +2548,16 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>AYACUCHO</t>
+          <t>CUSCO</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>HUANCARAYLLA</t>
+          <t>PICHARI</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>219</v>
+        <v>894</v>
       </c>
     </row>
     <row r="119">
@@ -2566,16 +2566,16 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>CAJAMARCA</t>
+          <t>CUSCO</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>ANDABAMBA</t>
+          <t>SAYLLA</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>17</v>
+        <v>121</v>
       </c>
     </row>
     <row r="120">
@@ -2584,16 +2584,16 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>CUSCO</t>
+          <t>HUANCAVELICA</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>PICHARI</t>
+          <t>HUAYACUNDO ARMA</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>1203</v>
+        <v>4</v>
       </c>
     </row>
     <row r="121">
@@ -2602,16 +2602,16 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>CUSCO</t>
+          <t>HUANCAVELICA</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>SAYLLA</t>
+          <t>PILCHACA</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>297</v>
+        <v>15</v>
       </c>
     </row>
     <row r="122">
@@ -2625,11 +2625,11 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>HUAYACUNDO ARMA</t>
+          <t>TAMBO</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>61</v>
+        <v>143</v>
       </c>
     </row>
     <row r="123">
@@ -2638,16 +2638,16 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>HUANCAVELICA</t>
+          <t>HUANUCO</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>PILCHACA</t>
+          <t>CAHUAC</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>27</v>
+        <v>61</v>
       </c>
     </row>
     <row r="124">
@@ -2656,16 +2656,16 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>HUANCAVELICA</t>
+          <t>HUANUCO</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>TAMBO</t>
+          <t>CASTILLO GRANDE</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>201</v>
+        <v>561</v>
       </c>
     </row>
     <row r="125">
@@ -2679,11 +2679,11 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>CAHUAC</t>
+          <t>CHACABAMBA</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>151</v>
+        <v>83</v>
       </c>
     </row>
     <row r="126">
@@ -2697,11 +2697,11 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>CASTILLO GRANDE</t>
+          <t>LA MORADA</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>809</v>
+        <v>98</v>
       </c>
     </row>
     <row r="127">
@@ -2715,11 +2715,11 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>CHACABAMBA</t>
+          <t>PAMPAMARCA</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>320</v>
+        <v>134</v>
       </c>
     </row>
     <row r="128">
@@ -2733,11 +2733,11 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>LA MORADA</t>
+          <t>SANTA ROSA DE ALTO YANAJANCA</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>176</v>
+        <v>59</v>
       </c>
     </row>
     <row r="129">
@@ -2751,11 +2751,11 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>PAMPAMARCA</t>
+          <t>YARUMAYO</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>166</v>
+        <v>28</v>
       </c>
     </row>
     <row r="130">
@@ -2764,16 +2764,16 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>HUANUCO</t>
+          <t>JUNIN</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>SANTA ROSA DE ALTO YANAJANCA</t>
+          <t>MARCAPOMACOCHA</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>72</v>
+        <v>211</v>
       </c>
     </row>
     <row r="131">
@@ -2782,16 +2782,16 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>HUANUCO</t>
+          <t>JUNIN</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>YARUMAYO</t>
+          <t>VIZCATAN DEL ENE</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>201</v>
+        <v>94</v>
       </c>
     </row>
     <row r="132">
@@ -2800,16 +2800,16 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>LIMA</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>MARCAPOMACOCHA</t>
+          <t>ALIS</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>214</v>
+        <v>76</v>
       </c>
     </row>
     <row r="133">
@@ -2818,16 +2818,16 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>LIMA</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>VIZCATAN DEL ENE</t>
+          <t>ALLAUCA</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>570</v>
+        <v>6</v>
       </c>
     </row>
     <row r="134">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>ALIS</t>
+          <t>CARANIA</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>76</v>
+        <v>20</v>
       </c>
     </row>
     <row r="135">
@@ -2859,11 +2859,11 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>ALLAUCA</t>
+          <t>HUAMPARA</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>106</v>
+        <v>17</v>
       </c>
     </row>
     <row r="136">
@@ -2877,11 +2877,11 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>AZANGARO</t>
+          <t>HUANGASCAR</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>75</v>
+        <v>134</v>
       </c>
     </row>
     <row r="137">
@@ -2895,11 +2895,11 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>CARANIA</t>
+          <t>PUTINZA</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="138">
@@ -2913,11 +2913,11 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>HUAMPARA</t>
+          <t>TOMAS</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="139">
@@ -2926,16 +2926,16 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>LIMA</t>
+          <t>LORETO</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>HUANGASCAR</t>
+          <t>SOPLIN</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>144</v>
+        <v>44</v>
       </c>
     </row>
     <row r="140">
@@ -2944,16 +2944,16 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>LIMA</t>
+          <t>LORETO</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>LARAOS</t>
+          <t>TAPICHE</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>113</v>
+        <v>1</v>
       </c>
     </row>
     <row r="141">
@@ -2962,16 +2962,16 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>LIMA</t>
+          <t>MADRE DE DIOS</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>PUTINZA</t>
+          <t>TAHUAMANU</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>33</v>
+        <v>68</v>
       </c>
     </row>
     <row r="142">
@@ -2980,16 +2980,16 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>LIMA</t>
+          <t>MOQUEGUA</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>TOMAS</t>
+          <t>EL ALGARROBAL</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>42</v>
+        <v>97</v>
       </c>
     </row>
     <row r="143">
@@ -2998,16 +2998,16 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>LORETO</t>
+          <t>PASCO</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>SOPLIN</t>
+          <t>CHACAYAN</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>160</v>
+        <v>196</v>
       </c>
     </row>
     <row r="144">
@@ -3016,16 +3016,16 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>LORETO</t>
+          <t>PASCO</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>TAPICHE</t>
+          <t>GOYLLARISQUIZGA</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>84</v>
+        <v>29</v>
       </c>
     </row>
     <row r="145">
@@ -3034,16 +3034,16 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>PUNO</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>TAHUAMANU</t>
+          <t>LIMBANI</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>105</v>
+        <v>139</v>
       </c>
     </row>
     <row r="146">
@@ -3052,16 +3052,16 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>MOQUEGUA</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>EL ALGARROBAL</t>
+          <t>SHUNTE</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>517</v>
+        <v>87</v>
       </c>
     </row>
     <row r="147">
@@ -3070,16 +3070,16 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>PASCO</t>
+          <t>TACNA</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>CHACAYAN</t>
+          <t>HEROES ALBARRACIN</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>196</v>
+        <v>82</v>
       </c>
     </row>
     <row r="148">
@@ -3088,16 +3088,16 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>PASCO</t>
+          <t>TACNA</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>GOYLLARISQUIZGA</t>
+          <t>ILABAYA</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>29</v>
+        <v>313</v>
       </c>
     </row>
     <row r="149">
@@ -3106,88 +3106,88 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>PUNO</t>
+          <t>TACNA</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>LIMBANI</t>
+          <t>SAMA</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>293</v>
+        <v>87</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="n">
-        <v>46095</v>
+        <v>46096</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>SAN MARTIN</t>
+          <t>AMAZONAS</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>SHUNTE</t>
+          <t>QUINJALCA</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>149</v>
+        <v>9</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="n">
-        <v>46095</v>
+        <v>46096</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>TACNA</t>
+          <t>ANCASH</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>HEROES ALBARRACIN</t>
+          <t>ANRA</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>83</v>
+        <v>4</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="n">
-        <v>46095</v>
+        <v>46096</v>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>TACNA</t>
+          <t>ANCASH</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>ILABAYA</t>
+          <t>CHAVIN DE HUANTAR</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>630</v>
+        <v>29</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="n">
-        <v>46095</v>
+        <v>46096</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>TACNA</t>
+          <t>ANCASH</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>SAMA</t>
+          <t>RAHUAPAMPA</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>153</v>
+        <v>1</v>
       </c>
     </row>
     <row r="154">
@@ -3196,16 +3196,16 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>AMAZONAS</t>
+          <t>ANCASH</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>QUINJALCA</t>
+          <t>SAN MARCOS</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="155">
@@ -3214,16 +3214,16 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>AMAZONAS</t>
+          <t>AREQUIPA</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>SONCHE</t>
+          <t>CHAPARRA</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
     </row>
     <row r="156">
@@ -3232,16 +3232,16 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>ANCASH</t>
+          <t>AREQUIPA</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>ANRA</t>
+          <t>MARIANO NICOLAS VALCARCEL</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>200</v>
+        <v>7</v>
       </c>
     </row>
     <row r="157">
@@ -3250,16 +3250,16 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>ANCASH</t>
+          <t>AREQUIPA</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>CHAVIN DE HUANTAR</t>
+          <t>QUEQUEÑA</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>1431</v>
+        <v>21</v>
       </c>
     </row>
     <row r="158">
@@ -3268,16 +3268,16 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>ANCASH</t>
+          <t>AYACUCHO</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>COTAPARACO</t>
+          <t>HUAC-HUAS</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="159">
@@ -3286,16 +3286,16 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>ANCASH</t>
+          <t>CUSCO</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>PONTO</t>
+          <t>PICHARI</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>528</v>
+        <v>65</v>
       </c>
     </row>
     <row r="160">
@@ -3304,16 +3304,16 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>ANCASH</t>
+          <t>HUANCAVELICA</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>RAHUAPAMPA</t>
+          <t>TAMBO</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>114</v>
+        <v>6</v>
       </c>
     </row>
     <row r="161">
@@ -3322,16 +3322,16 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>ANCASH</t>
+          <t>HUANUCO</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>SAN CRISTOBAL DE RAJAN</t>
+          <t>CASTILLO GRANDE</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>1</v>
+        <v>132</v>
       </c>
     </row>
     <row r="162">
@@ -3340,16 +3340,16 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>ANCASH</t>
+          <t>HUANUCO</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>SAN MARCOS</t>
+          <t>CHACABAMBA</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>2483</v>
+        <v>28</v>
       </c>
     </row>
     <row r="163">
@@ -3358,16 +3358,16 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>HUANUCO</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>CHAPARRA</t>
+          <t>PAMPAMARCA</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>138</v>
+        <v>7</v>
       </c>
     </row>
     <row r="164">
@@ -3376,16 +3376,16 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>HUANUCO</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>MARIANO NICOLAS VALCARCEL</t>
+          <t>SANTA ROSA DE ALTO YANAJANCA</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>412</v>
+        <v>6</v>
       </c>
     </row>
     <row r="165">
@@ -3394,16 +3394,16 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>JUNIN</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>MOLLEBAYA</t>
+          <t>MARCAPOMACOCHA</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>175</v>
+        <v>4</v>
       </c>
     </row>
     <row r="166">
@@ -3412,16 +3412,16 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>LIMA</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>QUEQUEÑA</t>
+          <t>HUAMPARA</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>268</v>
+        <v>30</v>
       </c>
     </row>
     <row r="167">
@@ -3430,16 +3430,16 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>MOQUEGUA</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>YARABAMBA</t>
+          <t>EL ALGARROBAL</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>371</v>
+        <v>1</v>
       </c>
     </row>
     <row r="168">
@@ -3448,16 +3448,16 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>AYACUCHO</t>
+          <t>PASCO</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>COLTA</t>
+          <t>CHACAYAN</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="169">
@@ -3466,16 +3466,16 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>AYACUCHO</t>
+          <t>PUNO</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>HUAC-HUAS</t>
+          <t>LIMBANI</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>150</v>
+        <v>3</v>
       </c>
     </row>
     <row r="170">
@@ -3484,1762 +3484,34 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>AYACUCHO</t>
+          <t>TACNA</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>HUANCARAYLLA</t>
+          <t>SAMA</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>230</v>
+        <v>5</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="n">
-        <v>46096</v>
+        <v>46097</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>CUSCO</t>
+          <t>HUANUCO</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>PICHARI</t>
+          <t>CASTILLO GRANDE</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>1225</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" s="2" t="n">
-        <v>46096</v>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>CUSCO</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>SAYLLA</t>
-        </is>
-      </c>
-      <c r="D172" t="n">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" s="2" t="n">
-        <v>46096</v>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>HUANCAVELICA</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>HUAYACUNDO ARMA</t>
-        </is>
-      </c>
-      <c r="D173" t="n">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" s="2" t="n">
-        <v>46096</v>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>HUANCAVELICA</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>PILCHACA</t>
-        </is>
-      </c>
-      <c r="D174" t="n">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" s="2" t="n">
-        <v>46096</v>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>HUANCAVELICA</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>TAMBO</t>
-        </is>
-      </c>
-      <c r="D175" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" s="2" t="n">
-        <v>46096</v>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>HUANUCO</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>CAHUAC</t>
-        </is>
-      </c>
-      <c r="D176" t="n">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" s="2" t="n">
-        <v>46096</v>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>HUANUCO</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>CASTILLO GRANDE</t>
-        </is>
-      </c>
-      <c r="D177" t="n">
-        <v>876</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" s="2" t="n">
-        <v>46096</v>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>HUANUCO</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>CHACABAMBA</t>
-        </is>
-      </c>
-      <c r="D178" t="n">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" s="2" t="n">
-        <v>46096</v>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>HUANUCO</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>LA MORADA</t>
-        </is>
-      </c>
-      <c r="D179" t="n">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" s="2" t="n">
-        <v>46096</v>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>HUANUCO</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>PAMPAMARCA</t>
-        </is>
-      </c>
-      <c r="D180" t="n">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" s="2" t="n">
-        <v>46096</v>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>HUANUCO</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>SANTA ROSA DE ALTO YANAJANCA</t>
-        </is>
-      </c>
-      <c r="D181" t="n">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" s="2" t="n">
-        <v>46096</v>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>HUANUCO</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>YARUMAYO</t>
-        </is>
-      </c>
-      <c r="D182" t="n">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" s="2" t="n">
-        <v>46096</v>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>JUNIN</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>MARCAPOMACOCHA</t>
-        </is>
-      </c>
-      <c r="D183" t="n">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" s="2" t="n">
-        <v>46096</v>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>JUNIN</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>VIZCATAN DEL ENE</t>
-        </is>
-      </c>
-      <c r="D184" t="n">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" s="2" t="n">
-        <v>46096</v>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>ALIS</t>
-        </is>
-      </c>
-      <c r="D185" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" s="2" t="n">
-        <v>46096</v>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>ALLAUCA</t>
-        </is>
-      </c>
-      <c r="D186" t="n">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" s="2" t="n">
-        <v>46096</v>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>AZANGARO</t>
-        </is>
-      </c>
-      <c r="D187" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" s="2" t="n">
-        <v>46096</v>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>HUAMPARA</t>
-        </is>
-      </c>
-      <c r="D188" t="n">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" s="2" t="n">
-        <v>46096</v>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>HUANGASCAR</t>
-        </is>
-      </c>
-      <c r="D189" t="n">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" s="2" t="n">
-        <v>46096</v>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>LARAOS</t>
-        </is>
-      </c>
-      <c r="D190" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" s="2" t="n">
-        <v>46096</v>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>PUTINZA</t>
-        </is>
-      </c>
-      <c r="D191" t="n">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" s="2" t="n">
-        <v>46096</v>
-      </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>TOMAS</t>
-        </is>
-      </c>
-      <c r="D192" t="n">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" s="2" t="n">
-        <v>46096</v>
-      </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>LORETO</t>
-        </is>
-      </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>SOPLIN</t>
-        </is>
-      </c>
-      <c r="D193" t="n">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" s="2" t="n">
-        <v>46096</v>
-      </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>LORETO</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>TAPICHE</t>
-        </is>
-      </c>
-      <c r="D194" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" s="2" t="n">
-        <v>46096</v>
-      </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>TAHUAMANU</t>
-        </is>
-      </c>
-      <c r="D195" t="n">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" s="2" t="n">
-        <v>46096</v>
-      </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>MOQUEGUA</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>EL ALGARROBAL</t>
-        </is>
-      </c>
-      <c r="D196" t="n">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" s="2" t="n">
-        <v>46096</v>
-      </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>PASCO</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>CHACAYAN</t>
-        </is>
-      </c>
-      <c r="D197" t="n">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" s="2" t="n">
-        <v>46096</v>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>PASCO</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>GOYLLARISQUIZGA</t>
-        </is>
-      </c>
-      <c r="D198" t="n">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" s="2" t="n">
-        <v>46096</v>
-      </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>LIMBANI</t>
-        </is>
-      </c>
-      <c r="D199" t="n">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" s="2" t="n">
-        <v>46096</v>
-      </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>SHUNTE</t>
-        </is>
-      </c>
-      <c r="D200" t="n">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" s="2" t="n">
-        <v>46096</v>
-      </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>HEROES ALBARRACIN</t>
-        </is>
-      </c>
-      <c r="D201" t="n">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" s="2" t="n">
-        <v>46096</v>
-      </c>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="C202" t="inlineStr">
-        <is>
-          <t>ILABAYA</t>
-        </is>
-      </c>
-      <c r="D202" t="n">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" s="2" t="n">
-        <v>46096</v>
-      </c>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>SAMA</t>
-        </is>
-      </c>
-      <c r="D203" t="n">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" s="2" t="n">
-        <v>46097</v>
-      </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>AMAZONAS</t>
-        </is>
-      </c>
-      <c r="C204" t="inlineStr">
-        <is>
-          <t>SONCHE</t>
-        </is>
-      </c>
-      <c r="D204" t="n">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" s="2" t="n">
-        <v>46097</v>
-      </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>ANCASH</t>
-        </is>
-      </c>
-      <c r="C205" t="inlineStr">
-        <is>
-          <t>ANRA</t>
-        </is>
-      </c>
-      <c r="D205" t="n">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" s="2" t="n">
-        <v>46097</v>
-      </c>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>ANCASH</t>
-        </is>
-      </c>
-      <c r="C206" t="inlineStr">
-        <is>
-          <t>CHAVIN DE HUANTAR</t>
-        </is>
-      </c>
-      <c r="D206" t="n">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" s="2" t="n">
-        <v>46097</v>
-      </c>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>ANCASH</t>
-        </is>
-      </c>
-      <c r="C207" t="inlineStr">
-        <is>
-          <t>COTAPARACO</t>
-        </is>
-      </c>
-      <c r="D207" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" s="2" t="n">
-        <v>46097</v>
-      </c>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>ANCASH</t>
-        </is>
-      </c>
-      <c r="C208" t="inlineStr">
-        <is>
-          <t>PONTO</t>
-        </is>
-      </c>
-      <c r="D208" t="n">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" s="2" t="n">
-        <v>46097</v>
-      </c>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>ANCASH</t>
-        </is>
-      </c>
-      <c r="C209" t="inlineStr">
-        <is>
-          <t>SAN MARCOS</t>
-        </is>
-      </c>
-      <c r="D209" t="n">
-        <v>949</v>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" s="2" t="n">
-        <v>46097</v>
-      </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr">
-        <is>
-          <t>CHAPARRA</t>
-        </is>
-      </c>
-      <c r="D210" t="n">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" s="2" t="n">
-        <v>46097</v>
-      </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr">
-        <is>
-          <t>MARIANO NICOLAS VALCARCEL</t>
-        </is>
-      </c>
-      <c r="D211" t="n">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" s="2" t="n">
-        <v>46097</v>
-      </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>MOLLEBAYA</t>
-        </is>
-      </c>
-      <c r="D212" t="n">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" s="2" t="n">
-        <v>46097</v>
-      </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>QUEQUEÑA</t>
-        </is>
-      </c>
-      <c r="D213" t="n">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" s="2" t="n">
-        <v>46097</v>
-      </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>YARABAMBA</t>
-        </is>
-      </c>
-      <c r="D214" t="n">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" s="2" t="n">
-        <v>46097</v>
-      </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>COLTA</t>
-        </is>
-      </c>
-      <c r="D215" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" s="2" t="n">
-        <v>46097</v>
-      </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>HUAC-HUAS</t>
-        </is>
-      </c>
-      <c r="D216" t="n">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" s="2" t="n">
-        <v>46097</v>
-      </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="C217" t="inlineStr">
-        <is>
-          <t>HUANCARAYLLA</t>
-        </is>
-      </c>
-      <c r="D217" t="n">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" s="2" t="n">
-        <v>46097</v>
-      </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>CUSCO</t>
-        </is>
-      </c>
-      <c r="C218" t="inlineStr">
-        <is>
-          <t>PICHARI</t>
-        </is>
-      </c>
-      <c r="D218" t="n">
-        <v>1414</v>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" s="2" t="n">
-        <v>46097</v>
-      </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>CUSCO</t>
-        </is>
-      </c>
-      <c r="C219" t="inlineStr">
-        <is>
-          <t>SAYLLA</t>
-        </is>
-      </c>
-      <c r="D219" t="n">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" s="2" t="n">
-        <v>46097</v>
-      </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>HUANCAVELICA</t>
-        </is>
-      </c>
-      <c r="C220" t="inlineStr">
-        <is>
-          <t>HUAYACUNDO ARMA</t>
-        </is>
-      </c>
-      <c r="D220" t="n">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" s="2" t="n">
-        <v>46097</v>
-      </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>HUANCAVELICA</t>
-        </is>
-      </c>
-      <c r="C221" t="inlineStr">
-        <is>
-          <t>PILCHACA</t>
-        </is>
-      </c>
-      <c r="D221" t="n">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" s="2" t="n">
-        <v>46097</v>
-      </c>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>HUANCAVELICA</t>
-        </is>
-      </c>
-      <c r="C222" t="inlineStr">
-        <is>
-          <t>TAMBO</t>
-        </is>
-      </c>
-      <c r="D222" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" s="2" t="n">
-        <v>46097</v>
-      </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>HUANUCO</t>
-        </is>
-      </c>
-      <c r="C223" t="inlineStr">
-        <is>
-          <t>CAHUAC</t>
-        </is>
-      </c>
-      <c r="D223" t="n">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" s="2" t="n">
-        <v>46097</v>
-      </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>HUANUCO</t>
-        </is>
-      </c>
-      <c r="C224" t="inlineStr">
-        <is>
-          <t>CASTILLO GRANDE</t>
-        </is>
-      </c>
-      <c r="D224" t="n">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" s="2" t="n">
-        <v>46097</v>
-      </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>HUANUCO</t>
-        </is>
-      </c>
-      <c r="C225" t="inlineStr">
-        <is>
-          <t>CHACABAMBA</t>
-        </is>
-      </c>
-      <c r="D225" t="n">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" s="2" t="n">
-        <v>46097</v>
-      </c>
-      <c r="B226" t="inlineStr">
-        <is>
-          <t>HUANUCO</t>
-        </is>
-      </c>
-      <c r="C226" t="inlineStr">
-        <is>
-          <t>LA MORADA</t>
-        </is>
-      </c>
-      <c r="D226" t="n">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" s="2" t="n">
-        <v>46097</v>
-      </c>
-      <c r="B227" t="inlineStr">
-        <is>
-          <t>HUANUCO</t>
-        </is>
-      </c>
-      <c r="C227" t="inlineStr">
-        <is>
-          <t>SANTA ROSA DE ALTO YANAJANCA</t>
-        </is>
-      </c>
-      <c r="D227" t="n">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" s="2" t="n">
-        <v>46097</v>
-      </c>
-      <c r="B228" t="inlineStr">
-        <is>
-          <t>HUANUCO</t>
-        </is>
-      </c>
-      <c r="C228" t="inlineStr">
-        <is>
-          <t>YARUMAYO</t>
-        </is>
-      </c>
-      <c r="D228" t="n">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" s="2" t="n">
-        <v>46097</v>
-      </c>
-      <c r="B229" t="inlineStr">
-        <is>
-          <t>JUNIN</t>
-        </is>
-      </c>
-      <c r="C229" t="inlineStr">
-        <is>
-          <t>MARCAPOMACOCHA</t>
-        </is>
-      </c>
-      <c r="D229" t="n">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" s="2" t="n">
-        <v>46097</v>
-      </c>
-      <c r="B230" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="C230" t="inlineStr">
-        <is>
-          <t>ALIS</t>
-        </is>
-      </c>
-      <c r="D230" t="n">
         <v>1</v>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" s="2" t="n">
-        <v>46097</v>
-      </c>
-      <c r="B231" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="C231" t="inlineStr">
-        <is>
-          <t>ALLAUCA</t>
-        </is>
-      </c>
-      <c r="D231" t="n">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" s="2" t="n">
-        <v>46097</v>
-      </c>
-      <c r="B232" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="C232" t="inlineStr">
-        <is>
-          <t>HUAMPARA</t>
-        </is>
-      </c>
-      <c r="D232" t="n">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" s="2" t="n">
-        <v>46097</v>
-      </c>
-      <c r="B233" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="C233" t="inlineStr">
-        <is>
-          <t>HUANGASCAR</t>
-        </is>
-      </c>
-      <c r="D233" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" s="2" t="n">
-        <v>46097</v>
-      </c>
-      <c r="B234" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="C234" t="inlineStr">
-        <is>
-          <t>PUTINZA</t>
-        </is>
-      </c>
-      <c r="D234" t="n">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" s="2" t="n">
-        <v>46097</v>
-      </c>
-      <c r="B235" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="C235" t="inlineStr">
-        <is>
-          <t>TOMAS</t>
-        </is>
-      </c>
-      <c r="D235" t="n">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" s="2" t="n">
-        <v>46097</v>
-      </c>
-      <c r="B236" t="inlineStr">
-        <is>
-          <t>LORETO</t>
-        </is>
-      </c>
-      <c r="C236" t="inlineStr">
-        <is>
-          <t>SOPLIN</t>
-        </is>
-      </c>
-      <c r="D236" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" s="2" t="n">
-        <v>46097</v>
-      </c>
-      <c r="B237" t="inlineStr">
-        <is>
-          <t>MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="C237" t="inlineStr">
-        <is>
-          <t>TAHUAMANU</t>
-        </is>
-      </c>
-      <c r="D237" t="n">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" s="2" t="n">
-        <v>46097</v>
-      </c>
-      <c r="B238" t="inlineStr">
-        <is>
-          <t>MOQUEGUA</t>
-        </is>
-      </c>
-      <c r="C238" t="inlineStr">
-        <is>
-          <t>EL ALGARROBAL</t>
-        </is>
-      </c>
-      <c r="D238" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" s="2" t="n">
-        <v>46097</v>
-      </c>
-      <c r="B239" t="inlineStr">
-        <is>
-          <t>PASCO</t>
-        </is>
-      </c>
-      <c r="C239" t="inlineStr">
-        <is>
-          <t>GOYLLARISQUIZGA</t>
-        </is>
-      </c>
-      <c r="D239" t="n">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" s="2" t="n">
-        <v>46097</v>
-      </c>
-      <c r="B240" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="C240" t="inlineStr">
-        <is>
-          <t>LIMBANI</t>
-        </is>
-      </c>
-      <c r="D240" t="n">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" s="2" t="n">
-        <v>46097</v>
-      </c>
-      <c r="B241" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="C241" t="inlineStr">
-        <is>
-          <t>SHUNTE</t>
-        </is>
-      </c>
-      <c r="D241" t="n">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" s="2" t="n">
-        <v>46097</v>
-      </c>
-      <c r="B242" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="C242" t="inlineStr">
-        <is>
-          <t>HEROES ALBARRACIN</t>
-        </is>
-      </c>
-      <c r="D242" t="n">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" s="2" t="n">
-        <v>46097</v>
-      </c>
-      <c r="B243" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="C243" t="inlineStr">
-        <is>
-          <t>ILABAYA</t>
-        </is>
-      </c>
-      <c r="D243" t="n">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" s="2" t="n">
-        <v>46097</v>
-      </c>
-      <c r="B244" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="C244" t="inlineStr">
-        <is>
-          <t>SAMA</t>
-        </is>
-      </c>
-      <c r="D244" t="n">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" s="2" t="n">
-        <v>46098</v>
-      </c>
-      <c r="B245" t="inlineStr">
-        <is>
-          <t>ANCASH</t>
-        </is>
-      </c>
-      <c r="C245" t="inlineStr">
-        <is>
-          <t>ANRA</t>
-        </is>
-      </c>
-      <c r="D245" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" s="2" t="n">
-        <v>46098</v>
-      </c>
-      <c r="B246" t="inlineStr">
-        <is>
-          <t>ANCASH</t>
-        </is>
-      </c>
-      <c r="C246" t="inlineStr">
-        <is>
-          <t>CHAVIN DE HUANTAR</t>
-        </is>
-      </c>
-      <c r="D246" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" s="2" t="n">
-        <v>46098</v>
-      </c>
-      <c r="B247" t="inlineStr">
-        <is>
-          <t>ANCASH</t>
-        </is>
-      </c>
-      <c r="C247" t="inlineStr">
-        <is>
-          <t>PONTO</t>
-        </is>
-      </c>
-      <c r="D247" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" s="2" t="n">
-        <v>46098</v>
-      </c>
-      <c r="B248" t="inlineStr">
-        <is>
-          <t>ANCASH</t>
-        </is>
-      </c>
-      <c r="C248" t="inlineStr">
-        <is>
-          <t>SAN MARCOS</t>
-        </is>
-      </c>
-      <c r="D248" t="n">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" s="2" t="n">
-        <v>46098</v>
-      </c>
-      <c r="B249" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="C249" t="inlineStr">
-        <is>
-          <t>MARIANO NICOLAS VALCARCEL</t>
-        </is>
-      </c>
-      <c r="D249" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" s="2" t="n">
-        <v>46098</v>
-      </c>
-      <c r="B250" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="C250" t="inlineStr">
-        <is>
-          <t>MOLLEBAYA</t>
-        </is>
-      </c>
-      <c r="D250" t="n">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" s="2" t="n">
-        <v>46098</v>
-      </c>
-      <c r="B251" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="C251" t="inlineStr">
-        <is>
-          <t>QUEQUEÑA</t>
-        </is>
-      </c>
-      <c r="D251" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" s="2" t="n">
-        <v>46098</v>
-      </c>
-      <c r="B252" t="inlineStr">
-        <is>
-          <t>AREQUIPA</t>
-        </is>
-      </c>
-      <c r="C252" t="inlineStr">
-        <is>
-          <t>YARABAMBA</t>
-        </is>
-      </c>
-      <c r="D252" t="n">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" s="2" t="n">
-        <v>46098</v>
-      </c>
-      <c r="B253" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="C253" t="inlineStr">
-        <is>
-          <t>COLTA</t>
-        </is>
-      </c>
-      <c r="D253" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" s="2" t="n">
-        <v>46098</v>
-      </c>
-      <c r="B254" t="inlineStr">
-        <is>
-          <t>AYACUCHO</t>
-        </is>
-      </c>
-      <c r="C254" t="inlineStr">
-        <is>
-          <t>HUAC-HUAS</t>
-        </is>
-      </c>
-      <c r="D254" t="n">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" s="2" t="n">
-        <v>46098</v>
-      </c>
-      <c r="B255" t="inlineStr">
-        <is>
-          <t>CUSCO</t>
-        </is>
-      </c>
-      <c r="C255" t="inlineStr">
-        <is>
-          <t>PICHARI</t>
-        </is>
-      </c>
-      <c r="D255" t="n">
-        <v>808</v>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" s="2" t="n">
-        <v>46098</v>
-      </c>
-      <c r="B256" t="inlineStr">
-        <is>
-          <t>CUSCO</t>
-        </is>
-      </c>
-      <c r="C256" t="inlineStr">
-        <is>
-          <t>SAYLLA</t>
-        </is>
-      </c>
-      <c r="D256" t="n">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" s="2" t="n">
-        <v>46098</v>
-      </c>
-      <c r="B257" t="inlineStr">
-        <is>
-          <t>HUANCAVELICA</t>
-        </is>
-      </c>
-      <c r="C257" t="inlineStr">
-        <is>
-          <t>PILCHACA</t>
-        </is>
-      </c>
-      <c r="D257" t="n">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" s="2" t="n">
-        <v>46098</v>
-      </c>
-      <c r="B258" t="inlineStr">
-        <is>
-          <t>HUANUCO</t>
-        </is>
-      </c>
-      <c r="C258" t="inlineStr">
-        <is>
-          <t>LA MORADA</t>
-        </is>
-      </c>
-      <c r="D258" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" s="2" t="n">
-        <v>46098</v>
-      </c>
-      <c r="B259" t="inlineStr">
-        <is>
-          <t>HUANUCO</t>
-        </is>
-      </c>
-      <c r="C259" t="inlineStr">
-        <is>
-          <t>SANTA ROSA DE ALTO YANAJANCA</t>
-        </is>
-      </c>
-      <c r="D259" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" s="2" t="n">
-        <v>46098</v>
-      </c>
-      <c r="B260" t="inlineStr">
-        <is>
-          <t>HUANUCO</t>
-        </is>
-      </c>
-      <c r="C260" t="inlineStr">
-        <is>
-          <t>YARUMAYO</t>
-        </is>
-      </c>
-      <c r="D260" t="n">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" s="2" t="n">
-        <v>46098</v>
-      </c>
-      <c r="B261" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="C261" t="inlineStr">
-        <is>
-          <t>ALIS</t>
-        </is>
-      </c>
-      <c r="D261" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" s="2" t="n">
-        <v>46098</v>
-      </c>
-      <c r="B262" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="C262" t="inlineStr">
-        <is>
-          <t>TOMAS</t>
-        </is>
-      </c>
-      <c r="D262" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" s="2" t="n">
-        <v>46098</v>
-      </c>
-      <c r="B263" t="inlineStr">
-        <is>
-          <t>MADRE DE DIOS</t>
-        </is>
-      </c>
-      <c r="C263" t="inlineStr">
-        <is>
-          <t>TAHUAMANU</t>
-        </is>
-      </c>
-      <c r="D263" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" s="2" t="n">
-        <v>46098</v>
-      </c>
-      <c r="B264" t="inlineStr">
-        <is>
-          <t>MOQUEGUA</t>
-        </is>
-      </c>
-      <c r="C264" t="inlineStr">
-        <is>
-          <t>EL ALGARROBAL</t>
-        </is>
-      </c>
-      <c r="D264" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" s="2" t="n">
-        <v>46098</v>
-      </c>
-      <c r="B265" t="inlineStr">
-        <is>
-          <t>PASCO</t>
-        </is>
-      </c>
-      <c r="C265" t="inlineStr">
-        <is>
-          <t>GOYLLARISQUIZGA</t>
-        </is>
-      </c>
-      <c r="D265" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" s="2" t="n">
-        <v>46098</v>
-      </c>
-      <c r="B266" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="C266" t="inlineStr">
-        <is>
-          <t>ILABAYA</t>
-        </is>
-      </c>
-      <c r="D266" t="n">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" s="2" t="n">
-        <v>46098</v>
-      </c>
-      <c r="B267" t="inlineStr">
-        <is>
-          <t>TACNA</t>
-        </is>
-      </c>
-      <c r="C267" t="inlineStr">
-        <is>
-          <t>SAMA</t>
-        </is>
-      </c>
-      <c r="D267" t="n">
-        <v>127</v>
       </c>
     </row>
   </sheetData>

--- a/data/data_distritos.xlsx
+++ b/data/data_distritos.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D171"/>
+  <dimension ref="A1:D272"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,7 +505,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="5">
@@ -523,7 +523,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>544</v>
+        <v>610</v>
       </c>
     </row>
     <row r="6">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7">
@@ -559,7 +559,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>154</v>
+        <v>552</v>
       </c>
     </row>
     <row r="8">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>24</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9">
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1034</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="10">
@@ -613,7 +613,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>127</v>
+        <v>143</v>
       </c>
     </row>
     <row r="11">
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="12">
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13">
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>30</v>
+        <v>52</v>
       </c>
     </row>
     <row r="14">
@@ -685,7 +685,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>38</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15">
@@ -775,7 +775,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>338</v>
+        <v>343</v>
       </c>
     </row>
     <row r="20">
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>85</v>
+        <v>93</v>
       </c>
     </row>
     <row r="25">
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>309</v>
+        <v>332</v>
       </c>
     </row>
     <row r="26">
@@ -901,7 +901,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>135</v>
+        <v>176</v>
       </c>
     </row>
     <row r="27">
@@ -919,7 +919,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>58</v>
+        <v>70</v>
       </c>
     </row>
     <row r="28">
@@ -933,11 +933,11 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>SANTA ROSA DE ALTO YANAJANCA</t>
+          <t>PAMPAMARCA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29">
@@ -951,11 +951,11 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>YARUMAYO</t>
+          <t>SANTA ROSA DE ALTO YANAJANCA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>167</v>
+        <v>24</v>
       </c>
     </row>
     <row r="30">
@@ -964,16 +964,16 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>HUANUCO</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>MARCAPOMACOCHA</t>
+          <t>YARUMAYO</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>178</v>
       </c>
     </row>
     <row r="31">
@@ -987,11 +987,11 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>VIZCATAN DEL ENE</t>
+          <t>MARCAPOMACOCHA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>68</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -1000,16 +1000,16 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>LIMA</t>
+          <t>JUNIN</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ALIS</t>
+          <t>VIZCATAN DEL ENE</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>19</v>
+        <v>152</v>
       </c>
     </row>
     <row r="33">
@@ -1023,11 +1023,11 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ALLAUCA</t>
+          <t>ALIS</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>148</v>
+        <v>20</v>
       </c>
     </row>
     <row r="34">
@@ -1041,11 +1041,11 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>AZANGARO</t>
+          <t>ALLAUCA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>48</v>
+        <v>261</v>
       </c>
     </row>
     <row r="35">
@@ -1059,11 +1059,11 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CARANIA</t>
+          <t>AZANGARO</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>24</v>
+        <v>126</v>
       </c>
     </row>
     <row r="36">
@@ -1077,11 +1077,11 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>HUAMPARA</t>
+          <t>CARANIA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="37">
@@ -1095,11 +1095,11 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>HUANGASCAR</t>
+          <t>HUAMPARA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -1113,11 +1113,11 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>LARAOS</t>
+          <t>HUANGASCAR</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="39">
@@ -1131,11 +1131,11 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>PUTINZA</t>
+          <t>LARAOS</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="40">
@@ -1149,11 +1149,11 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>TOMAS</t>
+          <t>PUTINZA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>34</v>
+        <v>16</v>
       </c>
     </row>
     <row r="41">
@@ -1162,16 +1162,16 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>LORETO</t>
+          <t>LIMA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>SOPLIN</t>
+          <t>TOMAS</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
     </row>
     <row r="42">
@@ -1185,11 +1185,11 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>TAPICHE</t>
+          <t>SOPLIN</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>173</v>
+        <v>51</v>
       </c>
     </row>
     <row r="43">
@@ -1198,16 +1198,16 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>LORETO</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>TAHUAMANU</t>
+          <t>TAPICHE</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>4</v>
+        <v>173</v>
       </c>
     </row>
     <row r="44">
@@ -1216,16 +1216,16 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>MOQUEGUA</t>
+          <t>MADRE DE DIOS</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>EL ALGARROBAL</t>
+          <t>TAHUAMANU</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>252</v>
+        <v>4</v>
       </c>
     </row>
     <row r="45">
@@ -1234,16 +1234,16 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>PASCO</t>
+          <t>MOQUEGUA</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>CHACAYAN</t>
+          <t>EL ALGARROBAL</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>14</v>
+        <v>268</v>
       </c>
     </row>
     <row r="46">
@@ -1257,11 +1257,11 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>GOYLLARISQUIZGA</t>
+          <t>CHACAYAN</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="47">
@@ -1270,16 +1270,16 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>PUNO</t>
+          <t>PASCO</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>LIMBANI</t>
+          <t>GOYLLARISQUIZGA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>77</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48">
@@ -1288,16 +1288,16 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SAN MARTIN</t>
+          <t>PUNO</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>SHUNTE</t>
+          <t>LIMBANI</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>86</v>
+        <v>77</v>
       </c>
     </row>
     <row r="49">
@@ -1306,16 +1306,16 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>TACNA</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ILABAYA</t>
+          <t>SHUNTE</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>145</v>
+        <v>86</v>
       </c>
     </row>
     <row r="50">
@@ -1329,29 +1329,29 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>SAMA</t>
+          <t>ILABAYA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>3</v>
+        <v>188</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>46094</v>
+        <v>46093</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>AMAZONAS</t>
+          <t>TACNA</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>QUINJALCA</t>
+          <t>SAMA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>38</v>
+        <v>18</v>
       </c>
     </row>
     <row r="52">
@@ -1365,11 +1365,11 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>SONCHE</t>
+          <t>QUINJALCA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>13</v>
+        <v>38</v>
       </c>
     </row>
     <row r="53">
@@ -1378,16 +1378,16 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ANCASH</t>
+          <t>AMAZONAS</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ANRA</t>
+          <t>SONCHE</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>200</v>
+        <v>13</v>
       </c>
     </row>
     <row r="54">
@@ -1401,11 +1401,11 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>CHAVIN DE HUANTAR</t>
+          <t>ANRA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1307</v>
+        <v>203</v>
       </c>
     </row>
     <row r="55">
@@ -1419,11 +1419,11 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>COTAPARACO</t>
+          <t>CHAVIN DE HUANTAR</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>31</v>
+        <v>1881</v>
       </c>
     </row>
     <row r="56">
@@ -1437,11 +1437,11 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>PONTO</t>
+          <t>COTAPARACO</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>244</v>
+        <v>31</v>
       </c>
     </row>
     <row r="57">
@@ -1455,11 +1455,11 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>RAHUAPAMPA</t>
+          <t>PONTO</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>70</v>
+        <v>489</v>
       </c>
     </row>
     <row r="58">
@@ -1473,11 +1473,11 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>SAN MARCOS</t>
+          <t>RAHUAPAMPA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>2541</v>
+        <v>157</v>
       </c>
     </row>
     <row r="59">
@@ -1486,16 +1486,16 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>ANCASH</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>CHAPARRA</t>
+          <t>SAN MARCOS</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>188</v>
+        <v>3524</v>
       </c>
     </row>
     <row r="60">
@@ -1509,11 +1509,11 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>MARIANO NICOLAS VALCARCEL</t>
+          <t>CHAPARRA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>390</v>
+        <v>231</v>
       </c>
     </row>
     <row r="61">
@@ -1527,11 +1527,11 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>MOLLEBAYA</t>
+          <t>MARIANO NICOLAS VALCARCEL</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>68</v>
+        <v>437</v>
       </c>
     </row>
     <row r="62">
@@ -1545,11 +1545,11 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>QUEQUEÑA</t>
+          <t>MOLLEBAYA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>152</v>
+        <v>105</v>
       </c>
     </row>
     <row r="63">
@@ -1563,11 +1563,11 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>YARABAMBA</t>
+          <t>QUEQUEÑA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>155</v>
+        <v>167</v>
       </c>
     </row>
     <row r="64">
@@ -1576,16 +1576,16 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>AYACUCHO</t>
+          <t>AREQUIPA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>COLTA</t>
+          <t>YARABAMBA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>101</v>
+        <v>209</v>
       </c>
     </row>
     <row r="65">
@@ -1599,11 +1599,11 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>HUAC-HUAS</t>
+          <t>COLTA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>75</v>
+        <v>102</v>
       </c>
     </row>
     <row r="66">
@@ -1617,11 +1617,11 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>HUANCARAYLLA</t>
+          <t>HUAC-HUAS</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>175</v>
+        <v>75</v>
       </c>
     </row>
     <row r="67">
@@ -1630,16 +1630,16 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>CAJAMARCA</t>
+          <t>AYACUCHO</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>ANDABAMBA</t>
+          <t>HUANCARAYLLA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11</v>
+        <v>175</v>
       </c>
     </row>
     <row r="68">
@@ -1648,16 +1648,16 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>CUSCO</t>
+          <t>CAJAMARCA</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>PICHARI</t>
+          <t>ANDABAMBA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>971</v>
+        <v>29</v>
       </c>
     </row>
     <row r="69">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>SAYLLA</t>
+          <t>PICHARI</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>233</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="70">
@@ -1684,16 +1684,16 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>HUANCAVELICA</t>
+          <t>CUSCO</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>HUAYACUNDO ARMA</t>
+          <t>SAYLLA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>39</v>
+        <v>233</v>
       </c>
     </row>
     <row r="71">
@@ -1707,11 +1707,11 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>PILCHACA</t>
+          <t>HUAYACUNDO ARMA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>12</v>
+        <v>39</v>
       </c>
     </row>
     <row r="72">
@@ -1725,11 +1725,11 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>TAMBO</t>
+          <t>PILCHACA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>82</v>
+        <v>19</v>
       </c>
     </row>
     <row r="73">
@@ -1738,16 +1738,16 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>HUANUCO</t>
+          <t>HUANCAVELICA</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>CAHUAC</t>
+          <t>TAMBO</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>117</v>
+        <v>82</v>
       </c>
     </row>
     <row r="74">
@@ -1761,11 +1761,11 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>CASTILLO GRANDE</t>
+          <t>CAHUAC</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>185</v>
+        <v>139</v>
       </c>
     </row>
     <row r="75">
@@ -1779,11 +1779,11 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>CHACABAMBA</t>
+          <t>CASTILLO GRANDE</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>166</v>
+        <v>199</v>
       </c>
     </row>
     <row r="76">
@@ -1797,11 +1797,11 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>LA MORADA</t>
+          <t>CHACABAMBA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>134</v>
+        <v>272</v>
       </c>
     </row>
     <row r="77">
@@ -1815,11 +1815,11 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>PAMPAMARCA</t>
+          <t>LA MORADA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>189</v>
+        <v>153</v>
       </c>
     </row>
     <row r="78">
@@ -1833,11 +1833,11 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>SANTA ROSA DE ALTO YANAJANCA</t>
+          <t>PAMPAMARCA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>13</v>
+        <v>189</v>
       </c>
     </row>
     <row r="79">
@@ -1851,11 +1851,11 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>YARUMAYO</t>
+          <t>SANTA ROSA DE ALTO YANAJANCA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>191</v>
+        <v>16</v>
       </c>
     </row>
     <row r="80">
@@ -1864,16 +1864,16 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>HUANUCO</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>MARCAPOMACOCHA</t>
+          <t>YARUMAYO</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>26</v>
+        <v>218</v>
       </c>
     </row>
     <row r="81">
@@ -1887,11 +1887,11 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>VIZCATAN DEL ENE</t>
+          <t>MARCAPOMACOCHA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>414</v>
+        <v>26</v>
       </c>
     </row>
     <row r="82">
@@ -1900,16 +1900,16 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>LIMA</t>
+          <t>JUNIN</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>ALIS</t>
+          <t>VIZCATAN DEL ENE</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>78</v>
+        <v>534</v>
       </c>
     </row>
     <row r="83">
@@ -1923,11 +1923,11 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>ALLAUCA</t>
+          <t>ALIS</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>18</v>
+        <v>80</v>
       </c>
     </row>
     <row r="84">
@@ -1941,11 +1941,11 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>CARANIA</t>
+          <t>ALLAUCA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>30</v>
+        <v>127</v>
       </c>
     </row>
     <row r="85">
@@ -1959,11 +1959,11 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>HUAMPARA</t>
+          <t>AZANGARO</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="86">
@@ -1977,11 +1977,11 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>HUANGASCAR</t>
+          <t>CARANIA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>85</v>
+        <v>30</v>
       </c>
     </row>
     <row r="87">
@@ -1995,11 +1995,11 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>LARAOS</t>
+          <t>HUAMPARA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>36</v>
+        <v>71</v>
       </c>
     </row>
     <row r="88">
@@ -2013,11 +2013,11 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>PUTINZA</t>
+          <t>HUANGASCAR</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>5</v>
+        <v>85</v>
       </c>
     </row>
     <row r="89">
@@ -2031,11 +2031,11 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>TOMAS</t>
+          <t>LARAOS</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="90">
@@ -2044,16 +2044,16 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>LORETO</t>
+          <t>LIMA</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>SOPLIN</t>
+          <t>PUTINZA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
     </row>
     <row r="91">
@@ -2062,16 +2062,16 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>LORETO</t>
+          <t>LIMA</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>TAPICHE</t>
+          <t>TOMAS</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>165</v>
+        <v>34</v>
       </c>
     </row>
     <row r="92">
@@ -2080,16 +2080,16 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>LORETO</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>TAHUAMANU</t>
+          <t>SOPLIN</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>70</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
@@ -2098,16 +2098,16 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>MOQUEGUA</t>
+          <t>LORETO</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>EL ALGARROBAL</t>
+          <t>TAPICHE</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>507</v>
+        <v>287</v>
       </c>
     </row>
     <row r="94">
@@ -2116,16 +2116,16 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>PASCO</t>
+          <t>MADRE DE DIOS</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>CHACAYAN</t>
+          <t>TAHUAMANU</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>102</v>
+        <v>70</v>
       </c>
     </row>
     <row r="95">
@@ -2134,16 +2134,16 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>PASCO</t>
+          <t>MOQUEGUA</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>GOYLLARISQUIZGA</t>
+          <t>EL ALGARROBAL</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>23</v>
+        <v>633</v>
       </c>
     </row>
     <row r="96">
@@ -2152,16 +2152,16 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>PUNO</t>
+          <t>PASCO</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>LIMBANI</t>
+          <t>CHACAYAN</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>175</v>
+        <v>102</v>
       </c>
     </row>
     <row r="97">
@@ -2170,16 +2170,16 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>SAN MARTIN</t>
+          <t>PASCO</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>SHUNTE</t>
+          <t>GOYLLARISQUIZGA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>204</v>
+        <v>23</v>
       </c>
     </row>
     <row r="98">
@@ -2188,16 +2188,16 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>TACNA</t>
+          <t>PUNO</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>HEROES ALBARRACIN</t>
+          <t>LIMBANI</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>135</v>
+        <v>175</v>
       </c>
     </row>
     <row r="99">
@@ -2206,16 +2206,16 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>TACNA</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>ILABAYA</t>
+          <t>SHUNTE</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>309</v>
+        <v>204</v>
       </c>
     </row>
     <row r="100">
@@ -2229,47 +2229,47 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>SAMA</t>
+          <t>HEROES ALBARRACIN</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>60</v>
+        <v>135</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>46095</v>
+        <v>46094</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>AMAZONAS</t>
+          <t>TACNA</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>QUINJALCA</t>
+          <t>ILABAYA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>76</v>
+        <v>565</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>46095</v>
+        <v>46094</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>AMAZONAS</t>
+          <t>TACNA</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>SONCHE</t>
+          <t>SAMA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>23</v>
+        <v>118</v>
       </c>
     </row>
     <row r="103">
@@ -2278,16 +2278,16 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>ANCASH</t>
+          <t>AMAZONAS</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>ANRA</t>
+          <t>QUINJALCA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>100</v>
+        <v>76</v>
       </c>
     </row>
     <row r="104">
@@ -2296,16 +2296,16 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>ANCASH</t>
+          <t>AMAZONAS</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>CHAVIN DE HUANTAR</t>
+          <t>SONCHE</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>544</v>
+        <v>25</v>
       </c>
     </row>
     <row r="105">
@@ -2319,11 +2319,11 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>COTAPARACO</t>
+          <t>ANRA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>49</v>
+        <v>246</v>
       </c>
     </row>
     <row r="106">
@@ -2337,11 +2337,11 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>PONTO</t>
+          <t>CHAVIN DE HUANTAR</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>30</v>
+        <v>2212</v>
       </c>
     </row>
     <row r="107">
@@ -2355,11 +2355,11 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>RAHUAPAMPA</t>
+          <t>COTAPARACO</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>21</v>
+        <v>49</v>
       </c>
     </row>
     <row r="108">
@@ -2373,11 +2373,11 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>SAN MARCOS</t>
+          <t>PONTO</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>991</v>
+        <v>410</v>
       </c>
     </row>
     <row r="109">
@@ -2386,16 +2386,16 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>ANCASH</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>CHAPARRA</t>
+          <t>RAHUAPAMPA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>47</v>
+        <v>99</v>
       </c>
     </row>
     <row r="110">
@@ -2404,16 +2404,16 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>ANCASH</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>MARIANO NICOLAS VALCARCEL</t>
+          <t>SAN MARCOS</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>63</v>
+        <v>3541</v>
       </c>
     </row>
     <row r="111">
@@ -2427,11 +2427,11 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>MOLLEBAYA</t>
+          <t>CHAPARRA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>157</v>
+        <v>151</v>
       </c>
     </row>
     <row r="112">
@@ -2445,11 +2445,11 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>QUEQUEÑA</t>
+          <t>MARIANO NICOLAS VALCARCEL</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>321</v>
+        <v>365</v>
       </c>
     </row>
     <row r="113">
@@ -2463,11 +2463,11 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>YARABAMBA</t>
+          <t>MOLLEBAYA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>264</v>
+        <v>331</v>
       </c>
     </row>
     <row r="114">
@@ -2476,16 +2476,16 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>AYACUCHO</t>
+          <t>AREQUIPA</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>COLTA</t>
+          <t>QUEQUEÑA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>50</v>
+        <v>343</v>
       </c>
     </row>
     <row r="115">
@@ -2494,16 +2494,16 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>AYACUCHO</t>
+          <t>AREQUIPA</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>HUAC-HUAS</t>
+          <t>YARABAMBA</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>125</v>
+        <v>486</v>
       </c>
     </row>
     <row r="116">
@@ -2517,11 +2517,11 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>HUANCARAYLLA</t>
+          <t>COLTA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>136</v>
+        <v>90</v>
       </c>
     </row>
     <row r="117">
@@ -2530,16 +2530,16 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>CAJAMARCA</t>
+          <t>AYACUCHO</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>ANDABAMBA</t>
+          <t>HUAC-HUAS</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>3</v>
+        <v>145</v>
       </c>
     </row>
     <row r="118">
@@ -2548,16 +2548,16 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>CUSCO</t>
+          <t>AYACUCHO</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>PICHARI</t>
+          <t>HUANCARAYLLA</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>894</v>
+        <v>219</v>
       </c>
     </row>
     <row r="119">
@@ -2566,16 +2566,16 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>CUSCO</t>
+          <t>CAJAMARCA</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>SAYLLA</t>
+          <t>ANDABAMBA</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>121</v>
+        <v>17</v>
       </c>
     </row>
     <row r="120">
@@ -2584,16 +2584,16 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>HUANCAVELICA</t>
+          <t>CUSCO</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>HUAYACUNDO ARMA</t>
+          <t>PICHARI</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>4</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="121">
@@ -2602,16 +2602,16 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>HUANCAVELICA</t>
+          <t>CUSCO</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>PILCHACA</t>
+          <t>SAYLLA</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>15</v>
+        <v>297</v>
       </c>
     </row>
     <row r="122">
@@ -2625,11 +2625,11 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>TAMBO</t>
+          <t>HUAYACUNDO ARMA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>143</v>
+        <v>61</v>
       </c>
     </row>
     <row r="123">
@@ -2638,16 +2638,16 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>HUANUCO</t>
+          <t>HUANCAVELICA</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>CAHUAC</t>
+          <t>PILCHACA</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>61</v>
+        <v>27</v>
       </c>
     </row>
     <row r="124">
@@ -2656,16 +2656,16 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>HUANUCO</t>
+          <t>HUANCAVELICA</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>CASTILLO GRANDE</t>
+          <t>TAMBO</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>561</v>
+        <v>201</v>
       </c>
     </row>
     <row r="125">
@@ -2679,11 +2679,11 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>CHACABAMBA</t>
+          <t>CAHUAC</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>83</v>
+        <v>151</v>
       </c>
     </row>
     <row r="126">
@@ -2697,11 +2697,11 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>LA MORADA</t>
+          <t>CASTILLO GRANDE</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>98</v>
+        <v>824</v>
       </c>
     </row>
     <row r="127">
@@ -2715,11 +2715,11 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>PAMPAMARCA</t>
+          <t>CHACABAMBA</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>134</v>
+        <v>321</v>
       </c>
     </row>
     <row r="128">
@@ -2733,11 +2733,11 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>SANTA ROSA DE ALTO YANAJANCA</t>
+          <t>LA MORADA</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>59</v>
+        <v>176</v>
       </c>
     </row>
     <row r="129">
@@ -2751,11 +2751,11 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>YARUMAYO</t>
+          <t>PAMPAMARCA</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>28</v>
+        <v>166</v>
       </c>
     </row>
     <row r="130">
@@ -2764,16 +2764,16 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>HUANUCO</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>MARCAPOMACOCHA</t>
+          <t>SANTA ROSA DE ALTO YANAJANCA</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>211</v>
+        <v>79</v>
       </c>
     </row>
     <row r="131">
@@ -2782,16 +2782,16 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>HUANUCO</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>VIZCATAN DEL ENE</t>
+          <t>YARUMAYO</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>94</v>
+        <v>201</v>
       </c>
     </row>
     <row r="132">
@@ -2800,16 +2800,16 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>LIMA</t>
+          <t>JUNIN</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>ALIS</t>
+          <t>MARCAPOMACOCHA</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>76</v>
+        <v>214</v>
       </c>
     </row>
     <row r="133">
@@ -2818,16 +2818,16 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>LIMA</t>
+          <t>JUNIN</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>ALLAUCA</t>
+          <t>VIZCATAN DEL ENE</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>6</v>
+        <v>570</v>
       </c>
     </row>
     <row r="134">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>CARANIA</t>
+          <t>ALIS</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>20</v>
+        <v>76</v>
       </c>
     </row>
     <row r="135">
@@ -2859,11 +2859,11 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>HUAMPARA</t>
+          <t>ALLAUCA</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>17</v>
+        <v>106</v>
       </c>
     </row>
     <row r="136">
@@ -2877,11 +2877,11 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>HUANGASCAR</t>
+          <t>AZANGARO</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>134</v>
+        <v>75</v>
       </c>
     </row>
     <row r="137">
@@ -2895,11 +2895,11 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>PUTINZA</t>
+          <t>CARANIA</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="138">
@@ -2913,11 +2913,11 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>TOMAS</t>
+          <t>HUAMPARA</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="139">
@@ -2926,16 +2926,16 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>LORETO</t>
+          <t>LIMA</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>SOPLIN</t>
+          <t>HUANGASCAR</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>44</v>
+        <v>144</v>
       </c>
     </row>
     <row r="140">
@@ -2944,16 +2944,16 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>LORETO</t>
+          <t>LIMA</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>TAPICHE</t>
+          <t>LARAOS</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>1</v>
+        <v>113</v>
       </c>
     </row>
     <row r="141">
@@ -2962,16 +2962,16 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>MADRE DE DIOS</t>
+          <t>LIMA</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>TAHUAMANU</t>
+          <t>PUTINZA</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>68</v>
+        <v>33</v>
       </c>
     </row>
     <row r="142">
@@ -2980,16 +2980,16 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>MOQUEGUA</t>
+          <t>LIMA</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>EL ALGARROBAL</t>
+          <t>TOMAS</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>97</v>
+        <v>42</v>
       </c>
     </row>
     <row r="143">
@@ -2998,16 +2998,16 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>PASCO</t>
+          <t>LORETO</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>CHACAYAN</t>
+          <t>SOPLIN</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>196</v>
+        <v>160</v>
       </c>
     </row>
     <row r="144">
@@ -3016,16 +3016,16 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>PASCO</t>
+          <t>LORETO</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>GOYLLARISQUIZGA</t>
+          <t>TAPICHE</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>29</v>
+        <v>84</v>
       </c>
     </row>
     <row r="145">
@@ -3034,16 +3034,16 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>PUNO</t>
+          <t>MADRE DE DIOS</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>LIMBANI</t>
+          <t>TAHUAMANU</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>139</v>
+        <v>105</v>
       </c>
     </row>
     <row r="146">
@@ -3052,16 +3052,16 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>SAN MARTIN</t>
+          <t>MOQUEGUA</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>SHUNTE</t>
+          <t>EL ALGARROBAL</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>87</v>
+        <v>526</v>
       </c>
     </row>
     <row r="147">
@@ -3070,16 +3070,16 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>TACNA</t>
+          <t>PASCO</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>HEROES ALBARRACIN</t>
+          <t>CHACAYAN</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>82</v>
+        <v>196</v>
       </c>
     </row>
     <row r="148">
@@ -3088,16 +3088,16 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>TACNA</t>
+          <t>PASCO</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>ILABAYA</t>
+          <t>GOYLLARISQUIZGA</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>313</v>
+        <v>29</v>
       </c>
     </row>
     <row r="149">
@@ -3106,88 +3106,88 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>TACNA</t>
+          <t>PUNO</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>SAMA</t>
+          <t>LIMBANI</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>87</v>
+        <v>293</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="n">
-        <v>46096</v>
+        <v>46095</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>AMAZONAS</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>QUINJALCA</t>
+          <t>SHUNTE</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>9</v>
+        <v>149</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="n">
-        <v>46096</v>
+        <v>46095</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>ANCASH</t>
+          <t>TACNA</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>ANRA</t>
+          <t>HEROES ALBARRACIN</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>4</v>
+        <v>83</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="n">
-        <v>46096</v>
+        <v>46095</v>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>ANCASH</t>
+          <t>TACNA</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>CHAVIN DE HUANTAR</t>
+          <t>ILABAYA</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>29</v>
+        <v>630</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="n">
-        <v>46096</v>
+        <v>46095</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>ANCASH</t>
+          <t>TACNA</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>RAHUAPAMPA</t>
+          <t>SAMA</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>1</v>
+        <v>154</v>
       </c>
     </row>
     <row r="154">
@@ -3196,16 +3196,16 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>ANCASH</t>
+          <t>AMAZONAS</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>SAN MARCOS</t>
+          <t>QUINJALCA</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="155">
@@ -3214,16 +3214,16 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>AMAZONAS</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>CHAPARRA</t>
+          <t>SONCHE</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
     </row>
     <row r="156">
@@ -3232,16 +3232,16 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>ANCASH</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>MARIANO NICOLAS VALCARCEL</t>
+          <t>ANRA</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>7</v>
+        <v>200</v>
       </c>
     </row>
     <row r="157">
@@ -3250,16 +3250,16 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>AREQUIPA</t>
+          <t>ANCASH</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>QUEQUEÑA</t>
+          <t>CHAVIN DE HUANTAR</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>21</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="158">
@@ -3268,16 +3268,16 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>AYACUCHO</t>
+          <t>ANCASH</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>HUAC-HUAS</t>
+          <t>COTAPARACO</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="159">
@@ -3286,16 +3286,16 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>CUSCO</t>
+          <t>ANCASH</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>PICHARI</t>
+          <t>PONTO</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>65</v>
+        <v>581</v>
       </c>
     </row>
     <row r="160">
@@ -3304,16 +3304,16 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>HUANCAVELICA</t>
+          <t>ANCASH</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>TAMBO</t>
+          <t>RAHUAPAMPA</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>6</v>
+        <v>114</v>
       </c>
     </row>
     <row r="161">
@@ -3322,16 +3322,16 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>HUANUCO</t>
+          <t>ANCASH</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>CASTILLO GRANDE</t>
+          <t>SAN CRISTOBAL DE RAJAN</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>132</v>
+        <v>1</v>
       </c>
     </row>
     <row r="162">
@@ -3340,16 +3340,16 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>HUANUCO</t>
+          <t>ANCASH</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>CHACABAMBA</t>
+          <t>SAN MARCOS</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>28</v>
+        <v>2484</v>
       </c>
     </row>
     <row r="163">
@@ -3358,16 +3358,16 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>HUANUCO</t>
+          <t>AREQUIPA</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>PAMPAMARCA</t>
+          <t>CHAPARRA</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>7</v>
+        <v>138</v>
       </c>
     </row>
     <row r="164">
@@ -3376,16 +3376,16 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>HUANUCO</t>
+          <t>AREQUIPA</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>SANTA ROSA DE ALTO YANAJANCA</t>
+          <t>MARIANO NICOLAS VALCARCEL</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>6</v>
+        <v>434</v>
       </c>
     </row>
     <row r="165">
@@ -3394,16 +3394,16 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>AREQUIPA</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>MARCAPOMACOCHA</t>
+          <t>MOLLEBAYA</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>4</v>
+        <v>175</v>
       </c>
     </row>
     <row r="166">
@@ -3412,16 +3412,16 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>LIMA</t>
+          <t>AREQUIPA</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>HUAMPARA</t>
+          <t>QUEQUEÑA</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>30</v>
+        <v>268</v>
       </c>
     </row>
     <row r="167">
@@ -3430,16 +3430,16 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>MOQUEGUA</t>
+          <t>AREQUIPA</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>EL ALGARROBAL</t>
+          <t>YARABAMBA</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>1</v>
+        <v>423</v>
       </c>
     </row>
     <row r="168">
@@ -3448,16 +3448,16 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>PASCO</t>
+          <t>AYACUCHO</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>CHACAYAN</t>
+          <t>COLTA</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="169">
@@ -3466,16 +3466,16 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>PUNO</t>
+          <t>AYACUCHO</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>LIMBANI</t>
+          <t>HUAC-HUAS</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>3</v>
+        <v>150</v>
       </c>
     </row>
     <row r="170">
@@ -3484,34 +3484,1852 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>TACNA</t>
+          <t>AYACUCHO</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>SAMA</t>
+          <t>HUANCARAYLLA</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>5</v>
+        <v>230</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="n">
+        <v>46096</v>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>CUSCO</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>PICHARI</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>1226</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="n">
+        <v>46096</v>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>CUSCO</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>SAYLLA</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="n">
+        <v>46096</v>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>HUAYACUNDO ARMA</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="n">
+        <v>46096</v>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>PILCHACA</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="n">
+        <v>46096</v>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>TAMBO</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="n">
+        <v>46096</v>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>CAHUAC</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="n">
+        <v>46096</v>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>CASTILLO GRANDE</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="n">
+        <v>46096</v>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>CHACABAMBA</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="n">
+        <v>46096</v>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>LA MORADA</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="n">
+        <v>46096</v>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>PAMPAMARCA</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="n">
+        <v>46096</v>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>SANTA ROSA DE ALTO YANAJANCA</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="n">
+        <v>46096</v>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>YARUMAYO</t>
+        </is>
+      </c>
+      <c r="D182" t="n">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="n">
+        <v>46096</v>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>MARCAPOMACOCHA</t>
+        </is>
+      </c>
+      <c r="D183" t="n">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="n">
+        <v>46096</v>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>VIZCATAN DEL ENE</t>
+        </is>
+      </c>
+      <c r="D184" t="n">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="n">
+        <v>46096</v>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>ALIS</t>
+        </is>
+      </c>
+      <c r="D185" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="n">
+        <v>46096</v>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>ALLAUCA</t>
+        </is>
+      </c>
+      <c r="D186" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="n">
+        <v>46096</v>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>AZANGARO</t>
+        </is>
+      </c>
+      <c r="D187" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="n">
+        <v>46096</v>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>HUAMPARA</t>
+        </is>
+      </c>
+      <c r="D188" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="n">
+        <v>46096</v>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>HUANGASCAR</t>
+        </is>
+      </c>
+      <c r="D189" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="n">
+        <v>46096</v>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>LARAOS</t>
+        </is>
+      </c>
+      <c r="D190" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="n">
+        <v>46096</v>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>PUTINZA</t>
+        </is>
+      </c>
+      <c r="D191" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="n">
+        <v>46096</v>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>TOMAS</t>
+        </is>
+      </c>
+      <c r="D192" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="n">
+        <v>46096</v>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>LORETO</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>SOPLIN</t>
+        </is>
+      </c>
+      <c r="D193" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="n">
+        <v>46096</v>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>LORETO</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>TAPICHE</t>
+        </is>
+      </c>
+      <c r="D194" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="n">
+        <v>46096</v>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>TAHUAMANU</t>
+        </is>
+      </c>
+      <c r="D195" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="n">
+        <v>46096</v>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>MOQUEGUA</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>EL ALGARROBAL</t>
+        </is>
+      </c>
+      <c r="D196" t="n">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="n">
+        <v>46096</v>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>PASCO</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>CHACAYAN</t>
+        </is>
+      </c>
+      <c r="D197" t="n">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="n">
+        <v>46096</v>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>PASCO</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>GOYLLARISQUIZGA</t>
+        </is>
+      </c>
+      <c r="D198" t="n">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="n">
+        <v>46096</v>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>LIMBANI</t>
+        </is>
+      </c>
+      <c r="D199" t="n">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="n">
+        <v>46096</v>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>SHUNTE</t>
+        </is>
+      </c>
+      <c r="D200" t="n">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="n">
+        <v>46096</v>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>HEROES ALBARRACIN</t>
+        </is>
+      </c>
+      <c r="D201" t="n">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="n">
+        <v>46096</v>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>ILABAYA</t>
+        </is>
+      </c>
+      <c r="D202" t="n">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="n">
+        <v>46096</v>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>SAMA</t>
+        </is>
+      </c>
+      <c r="D203" t="n">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="n">
         <v>46097</v>
       </c>
-      <c r="B171" t="inlineStr">
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>AMAZONAS</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>SONCHE</t>
+        </is>
+      </c>
+      <c r="D204" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>ANRA</t>
+        </is>
+      </c>
+      <c r="D205" t="n">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>CHAVIN DE HUANTAR</t>
+        </is>
+      </c>
+      <c r="D206" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>COTAPARACO</t>
+        </is>
+      </c>
+      <c r="D207" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>PONTO</t>
+        </is>
+      </c>
+      <c r="D208" t="n">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>SAN MARCOS</t>
+        </is>
+      </c>
+      <c r="D209" t="n">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>CHAPARRA</t>
+        </is>
+      </c>
+      <c r="D210" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>MARIANO NICOLAS VALCARCEL</t>
+        </is>
+      </c>
+      <c r="D211" t="n">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>MOLLEBAYA</t>
+        </is>
+      </c>
+      <c r="D212" t="n">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>QUEQUEÑA</t>
+        </is>
+      </c>
+      <c r="D213" t="n">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>YARABAMBA</t>
+        </is>
+      </c>
+      <c r="D214" t="n">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>COLTA</t>
+        </is>
+      </c>
+      <c r="D215" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>HUAC-HUAS</t>
+        </is>
+      </c>
+      <c r="D216" t="n">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>HUANCARAYLLA</t>
+        </is>
+      </c>
+      <c r="D217" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>CUSCO</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>PICHARI</t>
+        </is>
+      </c>
+      <c r="D218" t="n">
+        <v>1585</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>CUSCO</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>SAYLLA</t>
+        </is>
+      </c>
+      <c r="D219" t="n">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>HUAYACUNDO ARMA</t>
+        </is>
+      </c>
+      <c r="D220" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>PILCHACA</t>
+        </is>
+      </c>
+      <c r="D221" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>TAMBO</t>
+        </is>
+      </c>
+      <c r="D222" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B223" t="inlineStr">
         <is>
           <t>HUANUCO</t>
         </is>
       </c>
-      <c r="C171" t="inlineStr">
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>CAHUAC</t>
+        </is>
+      </c>
+      <c r="D223" t="n">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
         <is>
           <t>CASTILLO GRANDE</t>
         </is>
       </c>
-      <c r="D171" t="n">
+      <c r="D224" t="n">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>CHACABAMBA</t>
+        </is>
+      </c>
+      <c r="D225" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>LA MORADA</t>
+        </is>
+      </c>
+      <c r="D226" t="n">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>SANTA ROSA DE ALTO YANAJANCA</t>
+        </is>
+      </c>
+      <c r="D227" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>YARUMAYO</t>
+        </is>
+      </c>
+      <c r="D228" t="n">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>JUNIN</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>MARCAPOMACOCHA</t>
+        </is>
+      </c>
+      <c r="D229" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>ALIS</t>
+        </is>
+      </c>
+      <c r="D230" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>ALLAUCA</t>
+        </is>
+      </c>
+      <c r="D231" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>HUAMPARA</t>
+        </is>
+      </c>
+      <c r="D232" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>HUANGASCAR</t>
+        </is>
+      </c>
+      <c r="D233" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>PUTINZA</t>
+        </is>
+      </c>
+      <c r="D234" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>TOMAS</t>
+        </is>
+      </c>
+      <c r="D235" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>LORETO</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>SOPLIN</t>
+        </is>
+      </c>
+      <c r="D236" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>TAHUAMANU</t>
+        </is>
+      </c>
+      <c r="D237" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>MOQUEGUA</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>EL ALGARROBAL</t>
+        </is>
+      </c>
+      <c r="D238" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>PASCO</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>GOYLLARISQUIZGA</t>
+        </is>
+      </c>
+      <c r="D239" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>PUNO</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>LIMBANI</t>
+        </is>
+      </c>
+      <c r="D240" t="n">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>SHUNTE</t>
+        </is>
+      </c>
+      <c r="D241" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>HEROES ALBARRACIN</t>
+        </is>
+      </c>
+      <c r="D242" t="n">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>ILABAYA</t>
+        </is>
+      </c>
+      <c r="D243" t="n">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>SAMA</t>
+        </is>
+      </c>
+      <c r="D244" t="n">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>ANRA</t>
+        </is>
+      </c>
+      <c r="D245" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>CHAVIN DE HUANTAR</t>
+        </is>
+      </c>
+      <c r="D246" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>PONTO</t>
+        </is>
+      </c>
+      <c r="D247" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>SAN CRISTOBAL DE RAJAN</t>
+        </is>
+      </c>
+      <c r="D248" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>SAN MARCOS</t>
+        </is>
+      </c>
+      <c r="D249" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>SAN PEDRO</t>
+        </is>
+      </c>
+      <c r="D250" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>MARIANO NICOLAS VALCARCEL</t>
+        </is>
+      </c>
+      <c r="D251" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>MOLLEBAYA</t>
+        </is>
+      </c>
+      <c r="D252" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>QUEQUEÑA</t>
+        </is>
+      </c>
+      <c r="D253" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>AREQUIPA</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>YARABAMBA</t>
+        </is>
+      </c>
+      <c r="D254" t="n">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>COLTA</t>
+        </is>
+      </c>
+      <c r="D255" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>HUAC-HUAS</t>
+        </is>
+      </c>
+      <c r="D256" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>AYACUCHO</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>HUANCARAYLLA</t>
+        </is>
+      </c>
+      <c r="D257" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>CUSCO</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>PICHARI</t>
+        </is>
+      </c>
+      <c r="D258" t="n">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>CUSCO</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>SAYLLA</t>
+        </is>
+      </c>
+      <c r="D259" t="n">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>HUANCAVELICA</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>PILCHACA</t>
+        </is>
+      </c>
+      <c r="D260" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>CHACABAMBA</t>
+        </is>
+      </c>
+      <c r="D261" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>LA MORADA</t>
+        </is>
+      </c>
+      <c r="D262" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>SANTA ROSA DE ALTO YANAJANCA</t>
+        </is>
+      </c>
+      <c r="D263" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>YARUMAYO</t>
+        </is>
+      </c>
+      <c r="D264" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>ALIS</t>
+        </is>
+      </c>
+      <c r="D265" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>TOMAS</t>
+        </is>
+      </c>
+      <c r="D266" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>LORETO</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>SOPLIN</t>
+        </is>
+      </c>
+      <c r="D267" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>MADRE DE DIOS</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>TAHUAMANU</t>
+        </is>
+      </c>
+      <c r="D268" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>MOQUEGUA</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>EL ALGARROBAL</t>
+        </is>
+      </c>
+      <c r="D269" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>PASCO</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>GOYLLARISQUIZGA</t>
+        </is>
+      </c>
+      <c r="D270" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>ILABAYA</t>
+        </is>
+      </c>
+      <c r="D271" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>SAMA</t>
+        </is>
+      </c>
+      <c r="D272" t="n">
+        <v>246</v>
       </c>
     </row>
   </sheetData>

--- a/data/data_distritos.xlsx
+++ b/data/data_distritos.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D272"/>
+  <dimension ref="A1:D275"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1258</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="10">
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>332</v>
+        <v>338</v>
       </c>
     </row>
     <row r="26">
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>3524</v>
+        <v>3580</v>
       </c>
     </row>
     <row r="60">
@@ -1783,7 +1783,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>199</v>
+        <v>203</v>
       </c>
     </row>
     <row r="76">
@@ -2143,7 +2143,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>633</v>
+        <v>636</v>
       </c>
     </row>
     <row r="96">
@@ -2413,7 +2413,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>3541</v>
+        <v>3565</v>
       </c>
     </row>
     <row r="111">
@@ -2701,7 +2701,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>824</v>
+        <v>870</v>
       </c>
     </row>
     <row r="127">
@@ -2773,7 +2773,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="131">
@@ -3295,7 +3295,7 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>581</v>
+        <v>593</v>
       </c>
     </row>
     <row r="160">
@@ -3349,7 +3349,7 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>2484</v>
+        <v>2491</v>
       </c>
     </row>
     <row r="163">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>877</v>
+        <v>906</v>
       </c>
     </row>
     <row r="178">
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>70</v>
+        <v>84</v>
       </c>
     </row>
     <row r="182">
@@ -4015,7 +4015,7 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>393</v>
+        <v>453</v>
       </c>
     </row>
     <row r="200">
@@ -4177,7 +4177,7 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="209">
@@ -4357,7 +4357,7 @@
         </is>
       </c>
       <c r="D218" t="n">
-        <v>1585</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="219">
@@ -4519,7 +4519,7 @@
         </is>
       </c>
       <c r="D227" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="228">
@@ -4699,7 +4699,7 @@
         </is>
       </c>
       <c r="D237" t="n">
-        <v>51</v>
+        <v>147</v>
       </c>
     </row>
     <row r="238">
@@ -4753,7 +4753,7 @@
         </is>
       </c>
       <c r="D240" t="n">
-        <v>355</v>
+        <v>367</v>
       </c>
     </row>
     <row r="241">
@@ -4879,7 +4879,7 @@
         </is>
       </c>
       <c r="D247" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
     </row>
     <row r="248">
@@ -4897,7 +4897,7 @@
         </is>
       </c>
       <c r="D248" t="n">
-        <v>20</v>
+        <v>78</v>
       </c>
     </row>
     <row r="249">
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="D250" t="n">
-        <v>66</v>
+        <v>118</v>
       </c>
     </row>
     <row r="251">
@@ -5005,7 +5005,7 @@
         </is>
       </c>
       <c r="D254" t="n">
-        <v>506</v>
+        <v>599</v>
       </c>
     </row>
     <row r="255">
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="D263" t="n">
-        <v>40</v>
+        <v>78</v>
       </c>
     </row>
     <row r="264">
@@ -5221,7 +5221,7 @@
         </is>
       </c>
       <c r="D266" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="267">
@@ -5257,7 +5257,7 @@
         </is>
       </c>
       <c r="D268" t="n">
-        <v>4</v>
+        <v>27</v>
       </c>
     </row>
     <row r="269">
@@ -5330,6 +5330,60 @@
       </c>
       <c r="D272" t="n">
         <v>246</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="2" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>SAN CRISTOBAL DE RAJAN</t>
+        </is>
+      </c>
+      <c r="D273" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="2" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>SAN PEDRO</t>
+        </is>
+      </c>
+      <c r="D274" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="2" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>HUANUCO</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>SANTA ROSA DE ALTO YANAJANCA</t>
+        </is>
+      </c>
+      <c r="D275" t="n">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
